--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FE7C9E-0983-428A-93C6-C7B853D3A2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0801B6A1-09C1-4C7A-BA88-3284C6309D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="15" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="16" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="5월 2주차" sheetId="18" r:id="rId14"/>
     <sheet name="5월 3주차" sheetId="19" r:id="rId15"/>
     <sheet name="5월 4주차" sheetId="22" r:id="rId16"/>
+    <sheet name="5월 5주차" sheetId="23" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="235">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -912,6 +913,28 @@
   <si>
     <t>재완</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5월 25일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5월 26일</t>
+  </si>
+  <si>
+    <t>5월 27일</t>
+  </si>
+  <si>
+    <t>5월 28일</t>
+  </si>
+  <si>
+    <t>5월 29일</t>
+  </si>
+  <si>
+    <t>5월 30일</t>
+  </si>
+  <si>
+    <t>5월 31일</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1113,135 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="76">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2450,10 +2601,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3104,10 +3255,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3798,10 +3949,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4513,10 +4664,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5282,10 +5433,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6057,10 +6208,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6848,10 +6999,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7619,10 +7770,747 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="72"/>
+    <sortCondition descending="1" ref="I2:I25"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A2F66D-ECF3-4F2B-A781-87F563FD2918}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>8 (63%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="17" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>6 (67%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>6 (50%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="K4" s="21"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>5 (80%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (80%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="18" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>4 (75%)</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="18" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="18" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="18" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>4 (0%)</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="18" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="18" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="18" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>3 (100%)</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="18" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="18" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="18" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="19" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="19" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="19" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="20" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
+        <v>6 (67%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="20" t="str" cm="1">
+        <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A22" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="20" t="str" cm="1">
+        <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A23" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="20" t="str" cm="1">
+        <f t="array" ref="I23">IF(COUNTA(B23:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B23:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B23:H23)-LEN(SUBSTITUTE(B23:H23,"W","")))/SUMPRODUCT(LEN(B23:H23)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A24" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="20" t="str" cm="1">
+        <f t="array" ref="I24">IF(COUNTA(B24:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B24:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B24:H24)-LEN(SUBSTITUTE(B24:H24,"W","")))/SUMPRODUCT(LEN(B24:H24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A25" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="20" t="str" cm="1">
+        <f t="array" ref="I25">IF(COUNTA(B25:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B25:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B25:H25)-LEN(SUBSTITUTE(B25:H25,"W","")))/SUMPRODUCT(LEN(B25:H25)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A26" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="3" t="str" cm="1">
+        <f t="array" ref="B26">IF(COUNTA(B2:B25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B25)-LEN(SUBSTITUTE(B2:B25,"W","")))/SUMPRODUCT(LEN(B2:B25)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="C26" s="3" t="str" cm="1">
+        <f t="array" ref="C26">IF(COUNTA(C2:C25)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C25)-LEN(SUBSTITUTE(C2:C25,"W","")))/SUMPRODUCT(LEN(C2:C25)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="D26" s="7" t="str" cm="1">
+        <f t="array" ref="D26">IF(COUNTA(D2:D25)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D25)-LEN(SUBSTITUTE(D2:D25,"W","")))/SUMPRODUCT(LEN(D2:D25)),"0%")&amp;")")</f>
+        <v>11 (82%)</v>
+      </c>
+      <c r="E26" s="3" t="str" cm="1">
+        <f t="array" ref="E26">IF(COUNTA(E2:E25)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E25)-LEN(SUBSTITUTE(E2:E25,"W","")))/SUMPRODUCT(LEN(E2:E25)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="F26" s="3" t="str" cm="1">
+        <f t="array" ref="F26">IF(COUNTA(F2:F25)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F25)-LEN(SUBSTITUTE(F2:F25,"W","")))/SUMPRODUCT(LEN(F2:F25)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="G26" s="3" t="str" cm="1">
+        <f t="array" ref="G26">IF(COUNTA(G2:G25)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G25)-LEN(SUBSTITUTE(G2:G25,"W","")))/SUMPRODUCT(LEN(G2:G25)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="H26" s="3" t="str" cm="1">
+        <f t="array" ref="H26">IF(COUNTA(H2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H25)-LEN(SUBSTITUTE(H2:H25,"W","")))/SUMPRODUCT(LEN(H2:H25)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I26" s="1" t="str" cm="1">
+        <f t="array" ref="I26">IF(COUNTA(B2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H25)-LEN(SUBSTITUTE(B2:H25,"W","")))/SUMPRODUCT(LEN(B2:H25)),"0%")&amp;")")</f>
+        <v>71 (58%)</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K26" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8120,10 +9008,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="64"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8712,10 +9600,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10015,10 +10903,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10674,10 +11562,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11378,10 +12266,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12013,10 +12901,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12701,10 +13589,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0801B6A1-09C1-4C7A-BA88-3284C6309D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA587B7-B060-49D1-BD29-C8F0FDAC0B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="16" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="4170" yWindow="698" windowWidth="14220" windowHeight="12082" firstSheet="11" activeTab="16" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="235">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1113,103 +1113,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="76">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="64">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2601,10 +2505,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3255,10 +3159,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3949,10 +3853,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4664,10 +4568,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5433,10 +5337,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6208,10 +6112,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="8"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6999,10 +6903,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7770,10 +7674,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7848,10 +7752,12 @@
       <c r="G2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>8 (63%)</v>
+        <v>10 (50%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>189</v>
@@ -7914,10 +7820,12 @@
       <c r="G4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="21"/>
+      <c r="H4" s="21" t="s">
+        <v>48</v>
+      </c>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>6 (50%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>143</v>
@@ -7944,10 +7852,12 @@
       <c r="G5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (80%)</v>
+        <v>6 (67%)</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>163</v>
@@ -8000,10 +7910,12 @@
         <v>47</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="I7" s="18" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>4 (75%)</v>
+        <v>5 (80%)</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>146</v>
@@ -8028,10 +7940,12 @@
         <v>47</v>
       </c>
       <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="I8" s="18" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
+        <v>5 (40%)</v>
       </c>
       <c r="J8" s="16" t="s">
         <v>147</v>
@@ -8056,10 +7970,12 @@
         <v>48</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="I9" s="18" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
+        <v>5 (40%)</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>185</v>
@@ -8112,10 +8028,12 @@
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>4 (50%)</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>146</v>
@@ -8164,10 +8082,12 @@
       <c r="G13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>3 (100%)</v>
+        <v>4 (75%)</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>152</v>
@@ -8186,10 +8106,12 @@
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="H14" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="I14" s="18" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>2 (50%)</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>220</v>
@@ -8282,10 +8204,12 @@
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="H18" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I18" s="19" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J18" s="22" t="s">
         <v>167</v>
@@ -8338,10 +8262,12 @@
       <c r="G20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>7 (71%)</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>186</v>
@@ -8494,11 +8420,11 @@
       </c>
       <c r="H26" s="3" t="str" cm="1">
         <f t="array" ref="H26">IF(COUNTA(H2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H25)-LEN(SUBSTITUTE(H2:H25,"W","")))/SUMPRODUCT(LEN(H2:H25)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (33%)</v>
       </c>
       <c r="I26" s="1" t="str" cm="1">
         <f t="array" ref="I26">IF(COUNTA(B2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H25)-LEN(SUBSTITUTE(B2:H25,"W","")))/SUMPRODUCT(LEN(B2:H25)),"0%")&amp;")")</f>
-        <v>71 (58%)</v>
+        <v>83 (54%)</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>132</v>
@@ -8507,10 +8433,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9008,10 +8934,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="52"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9600,10 +9526,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10903,10 +10829,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11562,10 +11488,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12266,10 +12192,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12901,10 +12827,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13589,10 +13515,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA587B7-B060-49D1-BD29-C8F0FDAC0B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095B1A9E-3503-4EE7-AECA-2CDDF68D15E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="698" windowWidth="14220" windowHeight="12082" firstSheet="11" activeTab="16" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="16" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -1113,7 +1113,391 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="112">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2505,10 +2889,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="111"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="110"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="109"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="108"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3159,10 +3543,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="76"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3853,10 +4237,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="72"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4568,10 +4952,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5337,10 +5721,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6112,10 +6496,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="61"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6903,10 +7287,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7674,10 +8058,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7768,69 +8152,69 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="3"/>
+        <v>222</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>48</v>
+      </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="K3" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>48</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>7 (43%)</v>
+        <v>6 (67%)</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="K4" s="21"/>
+        <v>166</v>
+      </c>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="23" t="s">
@@ -7893,124 +8277,122 @@
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="18" t="str" cm="1">
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="17" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
         <v>5 (80%)</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="K7" s="7"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="18" t="str" cm="1">
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="17" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
         <v>5 (40%)</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="K8" s="7"/>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="18" t="str" cm="1">
+      <c r="B9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="17" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
         <v>5 (40%)</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="K9" s="7"/>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="25" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="7"/>
+        <v>47</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="I10" s="18" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>4 (0%)</v>
+        <v>4 (75%)</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>169</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="25" t="s">
@@ -8042,55 +8424,57 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="25" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="G12" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="18" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>4 (0%)</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="K12" s="7"/>
+        <v>148</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="25" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="E13" s="7"/>
-      <c r="F13" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="F13" s="7"/>
       <c r="G13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>48</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H13" s="7"/>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>4 (75%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="K13" s="7"/>
     </row>
@@ -8433,10 +8817,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8934,10 +9318,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="107"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="106"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="105"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="104"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9526,10 +9910,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="103"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="102"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="101"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="100"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10829,10 +11213,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="99"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="98"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="97"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="96"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11488,10 +11872,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="95"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="94"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="93"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="92"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12192,10 +12576,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="88"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12827,10 +13211,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="84"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13515,10 +13899,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="80"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095B1A9E-3503-4EE7-AECA-2CDDF68D15E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D8593-F8B4-423E-ACA0-180D286D9479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="16" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="5월 3주차" sheetId="19" r:id="rId15"/>
     <sheet name="5월 4주차" sheetId="22" r:id="rId16"/>
     <sheet name="5월 5주차" sheetId="23" r:id="rId17"/>
+    <sheet name="6월 1주차" sheetId="24" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="243">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -935,6 +936,31 @@
   </si>
   <si>
     <t>5월 31일</t>
+  </si>
+  <si>
+    <t>6월 1일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6월 2일</t>
+  </si>
+  <si>
+    <t>6월 3일</t>
+  </si>
+  <si>
+    <t>6월 4일</t>
+  </si>
+  <si>
+    <t>6월 5일</t>
+  </si>
+  <si>
+    <t>6월 6일</t>
+  </si>
+  <si>
+    <t>6월 7일</t>
+  </si>
+  <si>
+    <t>10 (50%)</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1050,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1109,11 +1135,26 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="112">
+  <dxfs count="74">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1135,6 +1176,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFF1A983"/>
           <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1172,321 +1221,9 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2889,10 +2626,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="111"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="110"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="109"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="108"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="66"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3543,10 +3280,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4237,10 +3974,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="30"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4952,10 +4689,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="26"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5721,10 +5458,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6496,10 +6233,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="61"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="18"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7287,10 +7024,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="14"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8058,10 +7795,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8817,10 +8554,732 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="70"/>
+    <sortCondition descending="1" ref="I2:I25"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669AFEDB-FD97-4EBA-AC1E-4B8AD2F8BA48}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>6 (67%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="17" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" s="21"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (0%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="17" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>4 (75%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="31" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>4 (75%)</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="32"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="31" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>4 (25%)</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" s="28"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="31" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>4 (100%)</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="K10" s="28"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="31" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="18" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="18" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="18" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="18" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="18" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="19" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="19" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="19" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="20" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="20" t="str" cm="1">
+        <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
+        <v>4 (25%)</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A22" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="20" t="str" cm="1">
+        <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A23" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="20" t="str" cm="1">
+        <f t="array" ref="I23">IF(COUNTA(B23:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B23:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B23:H23)-LEN(SUBSTITUTE(B23:H23,"W","")))/SUMPRODUCT(LEN(B23:H23)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A24" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="20" t="str" cm="1">
+        <f t="array" ref="I24">IF(COUNTA(B24:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B24:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B24:H24)-LEN(SUBSTITUTE(B24:H24,"W","")))/SUMPRODUCT(LEN(B24:H24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A25" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="20" t="str" cm="1">
+        <f t="array" ref="I25">IF(COUNTA(B25:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B25:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B25:H25)-LEN(SUBSTITUTE(B25:H25,"W","")))/SUMPRODUCT(LEN(B25:H25)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A26" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="3" t="str" cm="1">
+        <f t="array" ref="B26">IF(COUNTA(B2:B25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B25)-LEN(SUBSTITUTE(B2:B25,"W","")))/SUMPRODUCT(LEN(B2:B25)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="C26" s="3" t="str" cm="1">
+        <f t="array" ref="C26">IF(COUNTA(C2:C25)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C25)-LEN(SUBSTITUTE(C2:C25,"W","")))/SUMPRODUCT(LEN(C2:C25)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="D26" s="3" t="str" cm="1">
+        <f t="array" ref="D26">IF(COUNTA(D2:D25)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D25)-LEN(SUBSTITUTE(D2:D25,"W","")))/SUMPRODUCT(LEN(D2:D25)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="E26" s="3" t="str" cm="1">
+        <f t="array" ref="E26">IF(COUNTA(E2:E25)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E25)-LEN(SUBSTITUTE(E2:E25,"W","")))/SUMPRODUCT(LEN(E2:E25)),"0%")&amp;")")</f>
+        <v>12 (25%)</v>
+      </c>
+      <c r="F26" s="3" t="str" cm="1">
+        <f t="array" ref="F26">IF(COUNTA(F2:F25)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F25)-LEN(SUBSTITUTE(F2:F25,"W","")))/SUMPRODUCT(LEN(F2:F25)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="G26" s="28" t="str" cm="1">
+        <f t="array" ref="G26">IF(COUNTA(G2:G25)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G25)-LEN(SUBSTITUTE(G2:G25,"W","")))/SUMPRODUCT(LEN(G2:G25)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="H26" s="28" t="str" cm="1">
+        <f t="array" ref="H26">IF(COUNTA(H2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H25)-LEN(SUBSTITUTE(H2:H25,"W","")))/SUMPRODUCT(LEN(H2:H25)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I26" s="1" t="str" cm="1">
+        <f t="array" ref="I26">IF(COUNTA(B2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H25)-LEN(SUBSTITUTE(B2:H25,"W","")))/SUMPRODUCT(LEN(B2:H25)),"0%")&amp;")")</f>
+        <v>60 (47%)</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K26" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="8"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9318,10 +9777,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="107"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="106"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="105"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="104"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="62"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9910,10 +10369,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="103"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="102"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="101"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="100"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11213,10 +11672,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="99"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="98"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="97"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="96"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="54"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11872,10 +12331,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="95"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="94"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="93"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="92"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="50"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12576,10 +13035,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="91"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="90"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13211,10 +13670,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="87"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="86"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13899,10 +14358,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D8593-F8B4-423E-ACA0-180D286D9479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B4CBB2-57BE-4B3A-9E02-97C01CBBDC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="17" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="243">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -864,10 +864,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7 (29%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5월 18일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -961,6 +957,10 @@
   </si>
   <si>
     <t>10 (50%)</t>
+  </si>
+  <si>
+    <t>7 (57%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1050,7 +1050,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1135,26 +1135,23 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="95">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1224,6 +1221,174 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2626,10 +2791,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="87"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2926,7 +3091,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
@@ -2999,7 +3164,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A14" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9" t="s">
@@ -3074,7 +3239,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A17" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -3280,10 +3445,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="59"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3405,7 +3570,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>48</v>
@@ -3589,7 +3754,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>47</v>
@@ -3757,7 +3922,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9" t="s">
@@ -3974,10 +4139,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="32"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4032,7 +4197,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>47</v>
@@ -4128,7 +4293,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>48</v>
@@ -4248,7 +4413,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
@@ -4689,10 +4854,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="28"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="51"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4747,7 +4912,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>47</v>
@@ -4843,7 +5008,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>48</v>
@@ -4907,7 +5072,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5111,7 +5276,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -5458,10 +5623,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5516,7 +5681,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>48</v>
@@ -5852,7 +6017,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>48</v>
@@ -5878,7 +6043,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>48</v>
@@ -5958,7 +6123,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -6043,10 +6208,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>47</v>
@@ -6065,7 +6230,7 @@
       </c>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>7 (29%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>186</v>
@@ -6196,11 +6361,11 @@
       </c>
       <c r="B26" s="3" t="str" cm="1">
         <f t="array" ref="B26">IF(COUNTA(B2:B25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B25)-LEN(SUBSTITUTE(B2:B25,"W","")))/SUMPRODUCT(LEN(B2:B25)),"0%")&amp;")")</f>
-        <v>12 (42%)</v>
+        <v>12 (50%)</v>
       </c>
       <c r="C26" s="3" t="str" cm="1">
         <f t="array" ref="C26">IF(COUNTA(C2:C25)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C25)-LEN(SUBSTITUTE(C2:C25,"W","")))/SUMPRODUCT(LEN(C2:C25)),"0%")&amp;")")</f>
-        <v>12 (58%)</v>
+        <v>12 (67%)</v>
       </c>
       <c r="D26" s="3" t="str" cm="1">
         <f t="array" ref="D26">IF(COUNTA(D2:D25)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D25)-LEN(SUBSTITUTE(D2:D25,"W","")))/SUMPRODUCT(LEN(D2:D25)),"0%")&amp;")")</f>
@@ -6224,7 +6389,7 @@
       </c>
       <c r="I26" s="1" t="str" cm="1">
         <f t="array" ref="I26">IF(COUNTA(B2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H25)-LEN(SUBSTITUTE(B2:H25,"W","")))/SUMPRODUCT(LEN(B2:H25)),"0%")&amp;")")</f>
-        <v>83 (47%)</v>
+        <v>83 (49%)</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>132</v>
@@ -6233,10 +6398,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="43"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6291,7 +6456,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>48</v>
@@ -6695,7 +6860,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -6717,7 +6882,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9" t="s">
@@ -6855,7 +7020,7 @@
         <v>7 (71%)</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>125</v>
@@ -7024,10 +7189,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="16"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7050,25 +7215,25 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="B1" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>218</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>219</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>50</v>
@@ -7082,7 +7247,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>47</v>
@@ -7150,7 +7315,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>48</v>
@@ -7544,7 +7709,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -7600,7 +7765,7 @@
         <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>48</v>
@@ -7619,10 +7784,10 @@
       </c>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>7 (43%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>125</v>
@@ -7762,7 +7927,7 @@
       </c>
       <c r="C26" s="3" t="str" cm="1">
         <f t="array" ref="C26">IF(COUNTA(C2:C25)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C25)-LEN(SUBSTITUTE(C2:C25,"W","")))/SUMPRODUCT(LEN(C2:C25)),"0%")&amp;")")</f>
-        <v>12 (58%)</v>
+        <v>12 (67%)</v>
       </c>
       <c r="D26" s="3" t="str" cm="1">
         <f t="array" ref="D26">IF(COUNTA(D2:D25)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D25)-LEN(SUBSTITUTE(D2:D25,"W","")))/SUMPRODUCT(LEN(D2:D25)),"0%")&amp;")")</f>
@@ -7786,7 +7951,7 @@
       </c>
       <c r="I26" s="1" t="str" cm="1">
         <f t="array" ref="I26">IF(COUNTA(B2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H25)-LEN(SUBSTITUTE(B2:H25,"W","")))/SUMPRODUCT(LEN(B2:H25)),"0%")&amp;")")</f>
-        <v>84 (44%)</v>
+        <v>84 (45%)</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>132</v>
@@ -7795,10 +7960,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7821,25 +7986,25 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="B1" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>233</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>234</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>50</v>
@@ -7853,7 +8018,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>48</v>
@@ -7889,7 +8054,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>48</v>
@@ -8235,13 +8400,13 @@
         <v>2 (50%)</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K14" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="25" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>48</v>
@@ -8256,36 +8421,42 @@
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
         <v>1 (0%)</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="7" t="s">
         <v>168</v>
       </c>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A16" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="18" t="str" cm="1">
+      <c r="A16" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="19" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="K16" s="7"/>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>7</v>
+        <v>220</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9" t="s">
@@ -8296,47 +8467,43 @@
         <v>47</v>
       </c>
       <c r="F17" s="9"/>
-      <c r="G17" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I17" s="19" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
         <v>3 (67%)</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>69</v>
+        <v>167</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9" t="s">
-        <v>48</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="H18" s="9"/>
       <c r="I18" s="19" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
@@ -8391,7 +8558,7 @@
         <v>7 (71%)</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>125</v>
@@ -8554,10 +8721,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="19"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8580,25 +8747,25 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="B1" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="H1" s="28" t="s">
         <v>240</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>241</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>50</v>
@@ -8612,7 +8779,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>48</v>
@@ -8634,7 +8801,7 @@
         <v>6 (67%)</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>44</v>
@@ -8642,7 +8809,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>48</v>
@@ -8791,114 +8958,114 @@
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="31" t="str" cm="1">
+      <c r="B8" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="30" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
         <v>4 (75%)</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="32"/>
+      <c r="K8" s="31"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="31" t="str" cm="1">
+      <c r="B9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="30" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
         <v>4 (25%)</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="28"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="31" t="str" cm="1">
+      <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="30" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
         <v>4 (100%)</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="31" t="str" cm="1">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="30" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
         <v>3 (33%)</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="K11" s="28" t="s">
+      <c r="K11" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -8950,29 +9117,27 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="18" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="25" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -8985,64 +9150,66 @@
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>148</v>
+      <c r="J15" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A16" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="18" t="str" cm="1">
+      <c r="A16" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="19" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="K16" s="7"/>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9" t="s">
-        <v>47</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="19" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J17" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="K17" s="9" t="s">
-        <v>43</v>
+      <c r="K17" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>48</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
@@ -9051,91 +9218,93 @@
       <c r="H18" s="9"/>
       <c r="I18" s="19" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>69</v>
+        <v>166</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A19" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="19" t="str" cm="1">
+      <c r="A19" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>104</v>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="26" t="s">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>5 (20%)</v>
+        <v>4 (25%)</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="20" t="str" cm="1">
         <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>168</v>
@@ -9256,11 +9425,11 @@
         <f t="array" ref="F26">IF(COUNTA(F2:F25)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F25)-LEN(SUBSTITUTE(F2:F25,"W","")))/SUMPRODUCT(LEN(F2:F25)),"0%")&amp;")")</f>
         <v>12 (58%)</v>
       </c>
-      <c r="G26" s="28" t="str" cm="1">
+      <c r="G26" s="1" t="str" cm="1">
         <f t="array" ref="G26">IF(COUNTA(G2:G25)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G25)-LEN(SUBSTITUTE(G2:G25,"W","")))/SUMPRODUCT(LEN(G2:G25)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="H26" s="28" t="str" cm="1">
+      <c r="H26" s="1" t="str" cm="1">
         <f t="array" ref="H26">IF(COUNTA(H2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H25)-LEN(SUBSTITUTE(H2:H25,"W","")))/SUMPRODUCT(LEN(H2:H25)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
@@ -9777,10 +9946,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="83"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10369,10 +10538,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="79"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11562,7 +11731,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
@@ -11672,10 +11841,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="56"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="94"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="93"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="92"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="91"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12093,7 +12262,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A16" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -12168,7 +12337,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A19" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -12331,10 +12500,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="75"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12616,7 +12785,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
@@ -12825,7 +12994,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A19" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>47</v>
@@ -13035,10 +13204,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="71"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13337,7 +13506,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
@@ -13531,7 +13700,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A19" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>48</v>
@@ -13670,10 +13839,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="67"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13868,7 +14037,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
@@ -14054,7 +14223,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>48</v>
@@ -14267,7 +14436,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
@@ -14358,10 +14527,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B4CBB2-57BE-4B3A-9E02-97C01CBBDC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BDC72E-5F7E-4093-BAEC-6560D5DD6FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="17" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="243">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1151,7 +1151,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="95">
+  <dxfs count="119">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1261,6 +1261,198 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2791,10 +2983,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="90"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="88"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="118"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="117"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="116"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="115"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3445,10 +3637,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="83"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4139,10 +4331,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="56"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="79"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4854,10 +5046,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="75"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5623,10 +5815,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="48"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="71"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6178,91 +6370,91 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A19" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="19" t="str" cm="1">
+      <c r="A19" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>45</v>
+        <v>7 (57%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="H20" s="5"/>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>7 (57%)</v>
+        <v>2 (50%)</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H21" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
       <c r="I21" s="20" t="str" cm="1">
         <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>2 (0%)</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>207</v>
+        <v>166</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.6">
@@ -6398,10 +6590,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="63"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6730,301 +6922,301 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16" t="s">
-        <v>47</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>4 (100%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="K11" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="H12" s="7"/>
       <c r="I12" s="18" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
-      </c>
-      <c r="J12" s="16" t="s">
+        <v>3 (33%)</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="K12" s="10" t="s">
-        <v>169</v>
-      </c>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B13" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="C13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>48</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>150</v>
+        <v>2 (0%)</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="7"/>
+        <v>198</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="18" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="K14" s="7"/>
+        <v>166</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+        <v>221</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
       <c r="I15" s="18" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>210</v>
+        <v>155</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A16" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="18" t="str" cm="1">
+      <c r="A16" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="19" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>188</v>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="19" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
+        <v>3 (0%)</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="24" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" s="19" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>3 (0%)</v>
+        <v>2 (50%)</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>104</v>
+        <v>149</v>
+      </c>
+      <c r="K18" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="24" t="s">
-        <v>7</v>
+        <v>208</v>
       </c>
       <c r="B19" s="9"/>
-      <c r="C19" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="9"/>
+      <c r="H19" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="I19" s="19" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
         <v>2 (50%)</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>69</v>
+        <v>166</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A20" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I20" s="19" t="str" cm="1">
+      <c r="A20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>209</v>
+        <v>7 (71%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H21" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12" t="s">
         <v>47</v>
       </c>
       <c r="I21" s="20" t="str" cm="1">
         <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
-        <v>7 (71%)</v>
+        <v>4 (100%)</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A22" s="26" t="s">
@@ -7189,10 +7381,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7281,107 +7473,103 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>48</v>
+        <v>222</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>7 (71%)</v>
+        <v>6 (33%)</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="K3" s="21"/>
+        <v>162</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="23" t="s">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="D4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>6 (33%)</v>
+        <v>5 (80%)</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="23" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (80%)</v>
+        <v>5 (60%)</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6" s="23" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>48</v>
@@ -7389,47 +7577,47 @@
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="17" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>5 (40%)</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7" s="23" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
         <v>47</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I7" s="17" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
         <v>5 (40%)</v>
@@ -7441,28 +7629,28 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" s="23" t="s">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="H8" s="3" t="s">
         <v>48</v>
       </c>
       <c r="I8" s="17" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>5 (40%)</v>
+        <v>5 (20%)</v>
       </c>
       <c r="J8" s="21" t="s">
         <v>146</v>
@@ -7471,16 +7659,16 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="F9" s="3" t="s">
         <v>48</v>
       </c>
@@ -7492,65 +7680,63 @@
       </c>
       <c r="I9" s="17" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>5 (20%)</v>
+        <v>5 (0%)</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A10" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="17" t="str" cm="1">
+      <c r="A10" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="18" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>5 (0%)</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="K10" s="3"/>
+        <v>4 (25%)</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7"/>
       <c r="D11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
+        <v>4 (0%)</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>147</v>
@@ -7559,69 +7745,63 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>48</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="18" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>4 (0%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="K12" s="7"/>
+        <v>150</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>169</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>48</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -7630,132 +7810,144 @@
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
         <v>1 (0%)</v>
       </c>
-      <c r="J14" s="16" t="s">
-        <v>147</v>
+      <c r="J14" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="25" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="18" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>148</v>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>190</v>
       </c>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A16" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="18" t="str" cm="1">
+      <c r="A16" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="19" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="K16" s="7"/>
+        <v>4 (25%)</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>47</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="B17" s="9"/>
       <c r="C17" s="9"/>
-      <c r="D17" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="H17" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I17" s="19" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
+        <v>3 (100%)</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>69</v>
+        <v>149</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="24" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="E18" s="9"/>
       <c r="F18" s="9"/>
-      <c r="G18" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
       <c r="I18" s="19" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>3 (100%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A19" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="19" t="str" cm="1">
+      <c r="A19" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>104</v>
-      </c>
+        <v>7 (71%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="26" t="s">
@@ -7960,10 +8152,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8382,53 +8574,57 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16" t="s">
-        <v>47</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
       <c r="I14" s="18" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="K14" s="16"/>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A15" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="18" t="str" cm="1">
+      <c r="A15" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="19" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="K15" s="7"/>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="24" t="s">
-        <v>7</v>
+        <v>220</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9" t="s">
@@ -8439,56 +8635,50 @@
         <v>47</v>
       </c>
       <c r="F16" s="9"/>
-      <c r="G16" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I16" s="19" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
         <v>3 (67%)</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>69</v>
+        <v>167</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9" t="s">
-        <v>48</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="19" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>48</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
@@ -8497,72 +8687,74 @@
       <c r="H18" s="9"/>
       <c r="I18" s="19" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>205</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A19" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="19" t="str" cm="1">
+      <c r="A19" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>104</v>
+        <v>7 (71%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12" t="s">
         <v>47</v>
       </c>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>7 (71%)</v>
+        <v>2 (50%)</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="K20" s="12"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="26" t="s">
@@ -8959,72 +9151,70 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
       <c r="I8" s="30" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>4 (75%)</v>
+        <v>4 (25%)</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="K8" s="31"/>
+        <v>182</v>
+      </c>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="29" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="30" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
+        <v>4 (100%)</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
@@ -9034,49 +9224,47 @@
       <c r="H10" s="1"/>
       <c r="I10" s="30" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>4 (100%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J10" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A11" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="30" t="str" cm="1">
+      <c r="A11" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>41</v>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="25" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -9084,40 +9272,36 @@
       <c r="H12" s="7"/>
       <c r="I12" s="18" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>1 (100%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>21</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="25" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -9130,64 +9314,66 @@
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="J14" s="16" t="s">
-        <v>148</v>
+      <c r="J14" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A15" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="18" t="str" cm="1">
+      <c r="A15" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="19" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="K15" s="7"/>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9" t="s">
-        <v>47</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="19" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J16" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>43</v>
+      <c r="K16" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>48</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -9196,67 +9382,75 @@
       <c r="H17" s="9"/>
       <c r="I17" s="19" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>69</v>
+        <v>166</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A18" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="19" t="str" cm="1">
+      <c r="A18" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>104</v>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>5 (20%)</v>
+        <v>4 (75%)</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>125</v>
+        <v>155</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
@@ -9946,10 +10140,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="86"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="84"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="114"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="113"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="112"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="111"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10538,10 +10732,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="80"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="110"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="109"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="108"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="107"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11841,10 +12035,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="94"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="93"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="92"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="106"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="105"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="104"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="103"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12500,10 +12694,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="102"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="101"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="100"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="99"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13204,10 +13398,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="98"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="97"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="96"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="95"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13839,10 +14033,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="94"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="93"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="92"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="91"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14527,10 +14721,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="87"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BDC72E-5F7E-4093-BAEC-6560D5DD6FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18647CDC-82A8-4727-9DD8-E16D4FDBBC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="17" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="243">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1151,127 +1151,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="119">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="69">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1810,289 +1690,9 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2983,10 +2583,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="118"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="117"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="116"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="115"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3637,10 +3237,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="86"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="84"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4331,10 +3931,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="80"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5046,10 +4646,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5815,10 +5415,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6590,10 +6190,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="12"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7381,10 +6981,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="8"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8152,10 +7752,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8913,10 +8513,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8953,7 +8553,7 @@
       <c r="F1" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="13" t="s">
         <v>239</v>
       </c>
       <c r="H1" s="28" t="s">
@@ -8986,11 +8586,13 @@
       <c r="F2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>8 (63%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>241</v>
@@ -9018,11 +8620,13 @@
       <c r="F3" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="21" t="s">
+        <v>47</v>
+      </c>
       <c r="H3" s="21"/>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (67%)</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>186</v>
@@ -9080,11 +8684,13 @@
       <c r="F5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (40%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>149</v>
@@ -9110,11 +8716,13 @@
       <c r="F6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="17" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>5 (0%)</v>
+        <v>6 (0%)</v>
       </c>
       <c r="J6" s="21" t="s">
         <v>163</v>
@@ -9138,11 +8746,13 @@
       <c r="F7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="17" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>4 (75%)</v>
+        <v>5 (60%)</v>
       </c>
       <c r="J7" s="21" t="s">
         <v>146</v>
@@ -9150,32 +8760,34 @@
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="30" t="str" cm="1">
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="17" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
-      </c>
-      <c r="J8" s="31" t="s">
+        <v>5 (20%)</v>
+      </c>
+      <c r="J8" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="29" t="s">
@@ -9220,11 +8832,13 @@
       <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="30" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>4 (25%)</v>
       </c>
       <c r="J10" s="31" t="s">
         <v>154</v>
@@ -9332,11 +8946,13 @@
         <v>48</v>
       </c>
       <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="G15" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="H15" s="9"/>
       <c r="I15" s="19" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J15" s="22" t="s">
         <v>150</v>
@@ -9410,11 +9026,13 @@
       <c r="F18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>5 (20%)</v>
+        <v>6 (17%)</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>219</v>
@@ -9440,11 +9058,13 @@
         <v>48</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="H19" s="12"/>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>4 (75%)</v>
+        <v>5 (60%)</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>155</v>
@@ -9470,11 +9090,13 @@
         <v>48</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="H20" s="5"/>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
+        <v>5 (20%)</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>168</v>
@@ -9619,9 +9241,9 @@
         <f t="array" ref="F26">IF(COUNTA(F2:F25)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F25)-LEN(SUBSTITUTE(F2:F25,"W","")))/SUMPRODUCT(LEN(F2:F25)),"0%")&amp;")")</f>
         <v>12 (58%)</v>
       </c>
-      <c r="G26" s="1" t="str" cm="1">
+      <c r="G26" s="3" t="str" cm="1">
         <f t="array" ref="G26">IF(COUNTA(G2:G25)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G25)-LEN(SUBSTITUTE(G2:G25,"W","")))/SUMPRODUCT(LEN(G2:G25)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (25%)</v>
       </c>
       <c r="H26" s="1" t="str" cm="1">
         <f t="array" ref="H26">IF(COUNTA(H2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H25)-LEN(SUBSTITUTE(H2:H25,"W","")))/SUMPRODUCT(LEN(H2:H25)),"0%")&amp;")")</f>
@@ -9629,7 +9251,7 @@
       </c>
       <c r="I26" s="1" t="str" cm="1">
         <f t="array" ref="I26">IF(COUNTA(B2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H25)-LEN(SUBSTITUTE(B2:H25,"W","")))/SUMPRODUCT(LEN(B2:H25)),"0%")&amp;")")</f>
-        <v>60 (47%)</v>
+        <v>72 (43%)</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>132</v>
@@ -9638,11 +9260,11 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="8"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10140,10 +9762,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="114"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="113"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="112"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="111"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="56"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10732,10 +10354,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="110"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="109"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="108"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="107"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12035,10 +11657,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="106"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="105"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="104"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="103"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12694,10 +12316,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="102"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="101"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="100"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="99"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13398,10 +13020,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="98"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="97"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="96"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="95"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14033,10 +13655,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="94"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="93"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="92"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14721,10 +14343,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="90"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="88"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18647CDC-82A8-4727-9DD8-E16D4FDBBC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBCF56A-379C-4D6D-8F09-AC94A349704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="17" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -37,6 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2월 4주차'!$A$8:$I$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="246">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -960,6 +961,18 @@
   </si>
   <si>
     <t>7 (57%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몇잎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0607 길갑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1050,7 +1063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1135,23 +1148,11 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="69">
+  <dxfs count="85">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1173,6 +1174,142 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFF1A983"/>
           <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1690,14 +1827,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF8ED973"/>
           <bgColor rgb="FF000000"/>
@@ -2583,10 +2712,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="81"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3237,10 +3366,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3931,10 +4060,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="45"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4646,10 +4775,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5415,10 +5544,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6190,10 +6319,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="33"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6981,10 +7110,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="29"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7752,10 +7881,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8192,7 +8321,9 @@
       <c r="J14" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="7"/>
+      <c r="K14" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="24" t="s">
@@ -8513,10 +8644,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="21"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8556,7 +8687,7 @@
       <c r="G1" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="13" t="s">
         <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -8589,10 +8720,12 @@
       <c r="G2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>8 (63%)</v>
+        <v>10 (50%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>241</v>
@@ -8623,10 +8756,12 @@
       <c r="G3" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="21"/>
+      <c r="H3" s="21" t="s">
+        <v>47</v>
+      </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>7 (71%)</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>186</v>
@@ -8635,65 +8770,65 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="23" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>169</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="23" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
         <v>6 (50%)</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -8731,33 +8866,35 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7" s="23" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="E7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="17" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
         <v>5 (60%)</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K7" s="3"/>
+        <v>185</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" s="23" t="s">
@@ -8790,62 +8927,66 @@
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="17" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="30" t="str" cm="1">
-        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>4 (100%)</v>
-      </c>
-      <c r="J9" s="31" t="s">
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="17" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>5 (100%)</v>
+      </c>
+      <c r="J10" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="30" t="str" cm="1">
-        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="25" t="s">
@@ -8903,10 +9044,12 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>148</v>
@@ -8914,51 +9057,57 @@
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A14" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="18" t="str" cm="1">
+      <c r="A14" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="19" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="K14" s="7"/>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="24" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="B15" s="9"/>
-      <c r="C15" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="I15" s="19" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
@@ -9004,7 +9153,7 @@
         <v>166</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>104</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
@@ -9012,10 +9161,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>47</v>
@@ -9029,10 +9178,12 @@
       <c r="G18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>6 (17%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>219</v>
@@ -9061,10 +9212,12 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="12"/>
+      <c r="H19" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>155</v>
@@ -9093,10 +9246,12 @@
       <c r="G20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>5 (20%)</v>
+        <v>6 (33%)</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>168</v>
@@ -9223,11 +9378,11 @@
       </c>
       <c r="B26" s="3" t="str" cm="1">
         <f t="array" ref="B26">IF(COUNTA(B2:B25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B25)-LEN(SUBSTITUTE(B2:B25,"W","")))/SUMPRODUCT(LEN(B2:B25)),"0%")&amp;")")</f>
-        <v>12 (42%)</v>
+        <v>12 (50%)</v>
       </c>
       <c r="C26" s="3" t="str" cm="1">
         <f t="array" ref="C26">IF(COUNTA(C2:C25)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C25)-LEN(SUBSTITUTE(C2:C25,"W","")))/SUMPRODUCT(LEN(C2:C25)),"0%")&amp;")")</f>
-        <v>12 (58%)</v>
+        <v>12 (67%)</v>
       </c>
       <c r="D26" s="3" t="str" cm="1">
         <f t="array" ref="D26">IF(COUNTA(D2:D25)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D25)-LEN(SUBSTITUTE(D2:D25,"W","")))/SUMPRODUCT(LEN(D2:D25)),"0%")&amp;")")</f>
@@ -9245,13 +9400,13 @@
         <f t="array" ref="G26">IF(COUNTA(G2:G25)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G25)-LEN(SUBSTITUTE(G2:G25,"W","")))/SUMPRODUCT(LEN(G2:G25)),"0%")&amp;")")</f>
         <v>12 (25%)</v>
       </c>
-      <c r="H26" s="1" t="str" cm="1">
+      <c r="H26" s="3" t="str" cm="1">
         <f t="array" ref="H26">IF(COUNTA(H2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H25)-LEN(SUBSTITUTE(H2:H25,"W","")))/SUMPRODUCT(LEN(H2:H25)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (33%)</v>
       </c>
       <c r="I26" s="1" t="str" cm="1">
         <f t="array" ref="I26">IF(COUNTA(B2:H25)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H25))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H25)-LEN(SUBSTITUTE(B2:H25,"W","")))/SUMPRODUCT(LEN(B2:H25)),"0%")&amp;")")</f>
-        <v>72 (43%)</v>
+        <v>84 (44%)</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>132</v>
@@ -9260,11 +9415,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9762,10 +9916,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="77"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10354,10 +10508,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="73"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11657,10 +11811,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="69"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12316,10 +12470,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="65"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13020,10 +13174,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="61"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13655,10 +13809,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="57"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14343,10 +14497,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="53"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBCF56A-379C-4D6D-8F09-AC94A349704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9218C993-F295-4DD9-835A-09C4DA36BC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="11" activeTab="17" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="18" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -31,13 +31,13 @@
     <sheet name="5월 4주차" sheetId="22" r:id="rId16"/>
     <sheet name="5월 5주차" sheetId="23" r:id="rId17"/>
     <sheet name="6월 1주차" sheetId="24" r:id="rId18"/>
+    <sheet name="6월 2주차" sheetId="26" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2월 4주차'!$A$8:$I$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="255">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -974,6 +974,34 @@
   <si>
     <t>0607 길갑</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 (0%)</t>
+  </si>
+  <si>
+    <t>5 (100%)</t>
+  </si>
+  <si>
+    <t>6월 8일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6월 9일</t>
+  </si>
+  <si>
+    <t>6월 10일</t>
+  </si>
+  <si>
+    <t>6월 11일</t>
+  </si>
+  <si>
+    <t>6월 12일</t>
+  </si>
+  <si>
+    <t>6월 13일</t>
+  </si>
+  <si>
+    <t>6월 14일</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1148,11 +1176,26 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="85">
+  <dxfs count="68">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1174,142 +1217,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFF1A983"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2712,10 +2619,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="84"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3366,10 +3273,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4060,10 +3967,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="48"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4775,10 +4682,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5544,10 +5451,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6319,10 +6226,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="12"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7110,10 +7017,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="8"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7881,10 +7788,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8644,10 +8551,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9415,11 +9322,644 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I25"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F743AD08-6784-483A-95D1-653749ACADDF}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="30" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>2 (100%)</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="30" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>2 (100%)</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="K3" s="29"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="30" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>2 (0%)</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="30" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>2 (0%)</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="K5" s="31"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="30" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="30" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="29"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="30" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="K8" s="29"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="30" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="30" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="K11" s="29"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="K12" s="29"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="30" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="30" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="K15" s="29"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="20" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="20" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="20" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>2 (100%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="20" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="20" t="str" cm="1">
+        <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A22" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="20" t="str" cm="1">
+        <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A23" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="20" t="str" cm="1">
+        <f t="array" ref="I23">IF(COUNTA(B23:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B23:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B23:H23)-LEN(SUBSTITUTE(B23:H23,"W","")))/SUMPRODUCT(LEN(B23:H23)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A24" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="20" t="str" cm="1">
+        <f t="array" ref="I24">IF(COUNTA(B24:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B24:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B24:H24)-LEN(SUBSTITUTE(B24:H24,"W","")))/SUMPRODUCT(LEN(B24:H24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A25" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="3" t="str" cm="1">
+        <f t="array" ref="B25">IF(COUNTA(B2:B24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B24)-LEN(SUBSTITUTE(B2:B24,"W","")))/SUMPRODUCT(LEN(B2:B24)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="C25" s="3" t="str" cm="1">
+        <f t="array" ref="C25">IF(COUNTA(C2:C24)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C24)-LEN(SUBSTITUTE(C2:C24,"W","")))/SUMPRODUCT(LEN(C2:C24)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="D25" s="3" t="str" cm="1">
+        <f t="array" ref="D25">IF(COUNTA(D2:D24)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D24)-LEN(SUBSTITUTE(D2:D24,"W","")))/SUMPRODUCT(LEN(D2:D24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="E25" s="3" t="str" cm="1">
+        <f t="array" ref="E25">IF(COUNTA(E2:E24)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E24)-LEN(SUBSTITUTE(E2:E24,"W","")))/SUMPRODUCT(LEN(E2:E24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="F25" s="3" t="str" cm="1">
+        <f t="array" ref="F25">IF(COUNTA(F2:F24)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F24)-LEN(SUBSTITUTE(F2:F24,"W","")))/SUMPRODUCT(LEN(F2:F24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="G25" s="3" t="str" cm="1">
+        <f t="array" ref="G25">IF(COUNTA(G2:G24)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G24)-LEN(SUBSTITUTE(G2:G24,"W","")))/SUMPRODUCT(LEN(G2:G24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="H25" s="3" t="str" cm="1">
+        <f t="array" ref="H25">IF(COUNTA(H2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H24)-LEN(SUBSTITUTE(H2:H24,"W","")))/SUMPRODUCT(LEN(H2:H24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I25" s="1" t="str" cm="1">
+        <f t="array" ref="I25">IF(COUNTA(B2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H24)-LEN(SUBSTITUTE(B2:H24,"W","")))/SUMPRODUCT(LEN(B2:H24)),"0%")&amp;")")</f>
+        <v>24 (54%)</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K25" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K16">
+    <sortCondition descending="1" ref="I2:I16"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9916,10 +10456,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="80"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="56"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10508,10 +11048,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11811,10 +12351,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12470,10 +13010,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13174,10 +13714,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13809,10 +14349,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14497,10 +15037,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9218C993-F295-4DD9-835A-09C4DA36BC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0874ECED-82E9-4C79-8A36-769846A7529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="18" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="255">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1091,7 +1091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1176,19 +1176,16 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2619,10 +2616,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3273,10 +3270,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3967,10 +3964,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4682,10 +4679,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5451,10 +5448,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6226,10 +6223,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7017,10 +7014,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="12"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7788,10 +7785,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="8"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8551,10 +8548,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9322,10 +9319,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9353,7 +9350,7 @@
       <c r="C1" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>250</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -9382,73 +9379,77 @@
       <c r="A2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="30" t="str" cm="1">
+      <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="29" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
-      </c>
-      <c r="J2" s="31" t="s">
+        <v>3 (67%)</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="K2" s="29"/>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="30" t="str" cm="1">
+      <c r="B3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="29" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
-      </c>
-      <c r="J3" s="31" t="s">
+        <v>3 (67%)</v>
+      </c>
+      <c r="J3" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="K3" s="29"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="30" t="str" cm="1">
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="29" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
         <v>2 (0%)</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9456,47 +9457,51 @@
       <c r="A5" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="30" t="str" cm="1">
+      <c r="B5" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="29" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
-      </c>
-      <c r="J5" s="31" t="s">
+        <v>3 (0%)</v>
+      </c>
+      <c r="J5" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="K5" s="31"/>
+      <c r="K5" s="30"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30" t="str" cm="1">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="29" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>1 (100%)</v>
-      </c>
-      <c r="J6" s="31" t="s">
+        <v>2 (100%)</v>
+      </c>
+      <c r="J6" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="31" t="s">
         <v>169</v>
       </c>
     </row>
@@ -9504,67 +9509,71 @@
       <c r="A7" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="30" t="str" cm="1">
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="29" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>1 (100%)</v>
-      </c>
-      <c r="J7" s="31" t="s">
+        <v>2 (50%)</v>
+      </c>
+      <c r="J7" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="K7" s="29"/>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="30" t="str" cm="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="29" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>1 (100%)</v>
-      </c>
-      <c r="J8" s="31" t="s">
+        <v>2 (100%)</v>
+      </c>
+      <c r="J8" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="K8" s="29"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30" t="str" cm="1">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="29" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
         <v>1 (100%)</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -9572,23 +9581,23 @@
       <c r="A10" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30" t="str" cm="1">
+      <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="29" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
         <v>1 (100%)</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="1" t="s">
         <v>245</v>
       </c>
     </row>
@@ -9596,67 +9605,71 @@
       <c r="A11" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="30" t="str" cm="1">
+      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="29" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J11" s="31" t="s">
+        <v>2 (50%)</v>
+      </c>
+      <c r="J11" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="K11" s="29"/>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30" t="str" cm="1">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="29" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J12" s="31" t="s">
+        <v>2 (0%)</v>
+      </c>
+      <c r="J12" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="K12" s="29"/>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30" t="str" cm="1">
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="29" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
         <v>1 (0%)</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K13" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -9664,23 +9677,23 @@
       <c r="A14" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30" t="str" cm="1">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="29" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
         <v>1 (0%)</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="32" t="s">
+      <c r="K14" s="31" t="s">
         <v>69</v>
       </c>
     </row>
@@ -9688,41 +9701,41 @@
       <c r="A15" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="30" t="str" cm="1">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="29" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="J15" s="31" t="s">
+      <c r="J15" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="K15" s="29"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30" t="str" cm="1">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="29" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="J16" s="31" t="s">
+      <c r="J16" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K16" s="1" t="s">
         <v>244</v>
       </c>
     </row>
@@ -9736,14 +9749,16 @@
       <c r="C17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="D17" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="20" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J17" s="12" t="s">
         <v>186</v>
@@ -9762,14 +9777,16 @@
       <c r="C18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>162</v>
@@ -9788,14 +9805,16 @@
       <c r="C19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>189</v>
@@ -9928,9 +9947,9 @@
         <f t="array" ref="C25">IF(COUNTA(C2:C24)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C24)-LEN(SUBSTITUTE(C2:C24,"W","")))/SUMPRODUCT(LEN(C2:C24)),"0%")&amp;")")</f>
         <v>12 (67%)</v>
       </c>
-      <c r="D25" s="3" t="str" cm="1">
+      <c r="D25" s="7" t="str" cm="1">
         <f t="array" ref="D25">IF(COUNTA(D2:D24)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D24)-LEN(SUBSTITUTE(D2:D24,"W","")))/SUMPRODUCT(LEN(D2:D24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>11 (36%)</v>
       </c>
       <c r="E25" s="3" t="str" cm="1">
         <f t="array" ref="E25">IF(COUNTA(E2:E24)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E24)-LEN(SUBSTITUTE(E2:E24,"W","")))/SUMPRODUCT(LEN(E2:E24)),"0%")&amp;")")</f>
@@ -9950,7 +9969,7 @@
       </c>
       <c r="I25" s="1" t="str" cm="1">
         <f t="array" ref="I25">IF(COUNTA(B2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H24)-LEN(SUBSTITUTE(B2:H24,"W","")))/SUMPRODUCT(LEN(B2:H24)),"0%")&amp;")")</f>
-        <v>24 (54%)</v>
+        <v>35 (49%)</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>132</v>
@@ -10456,10 +10475,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="60"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11048,10 +11067,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12351,10 +12370,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13010,10 +13029,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13714,10 +13733,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14349,10 +14368,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15037,10 +15056,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0874ECED-82E9-4C79-8A36-769846A7529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1048D52B-11E5-4AFB-9C90-5FF958F67FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="18" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="255">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1192,7 +1192,151 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="86">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2616,10 +2760,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="82"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3270,10 +3414,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3964,10 +4108,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="46"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4679,10 +4823,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5448,10 +5592,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6223,10 +6367,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="34"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7014,10 +7158,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7785,10 +7929,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8548,10 +8692,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="22"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9319,10 +9463,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9376,366 +9520,404 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="29" t="str" cm="1">
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
-      </c>
-      <c r="J2" s="30" t="s">
+        <v>5 (60%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="K2" s="1"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="29" t="str" cm="1">
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
-      </c>
-      <c r="J3" s="30" t="s">
+        <v>5 (60%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>5 (0%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="K4" s="21"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="29" t="str" cm="1">
-        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
-      </c>
-      <c r="J4" s="30" t="s">
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>4 (0%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K5" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A5" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="str" cm="1">
-        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>3 (0%)</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="K5" s="30"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6" s="28" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="29" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
+        <v>4 (25%)</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="K6" s="31" t="s">
-        <v>169</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="29" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>4 (100%)</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+        <v>243</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="29" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J8" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="28" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="29" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>1 (100%)</v>
+        <v>3 (100%)</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A10" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="29" t="str" cm="1">
+      <c r="A10" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="18" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>1 (100%)</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>245</v>
-      </c>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="29" t="str" cm="1">
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
         <v>2 (50%)</v>
       </c>
-      <c r="J11" s="30" t="s">
+      <c r="J11" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A12" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="29" t="str" cm="1">
+      <c r="A12" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="18" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="19" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="19" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="19" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
         <v>2 (0%)</v>
       </c>
-      <c r="J12" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A13" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="29" t="str" cm="1">
-        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J13" s="30" t="s">
+      <c r="J15" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K15" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A14" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="29" t="str" cm="1">
-        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A15" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="29" t="str" cm="1">
-        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J15" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="K15" s="1"/>
-    </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="29" t="str" cm="1">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="19" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="J16" s="30" t="s">
+      <c r="J16" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="9" t="s">
         <v>244</v>
       </c>
     </row>
@@ -9752,13 +9934,17 @@
       <c r="D17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="20" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>5 (80%)</v>
       </c>
       <c r="J17" s="12" t="s">
         <v>186</v>
@@ -9769,65 +9955,75 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>5 (60%)</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>201</v>
+        <v>189</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>5 (40%)</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>89</v>
+        <v>162</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="5"/>
+        <v>85</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -9836,10 +10032,10 @@
       <c r="H20" s="5"/>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>89</v>
@@ -9847,7 +10043,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="26" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -9861,19 +10057,17 @@
         <v>0 (0%)</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>170</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A22" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -9882,13 +10076,13 @@
       <c r="H22" s="5"/>
       <c r="I22" s="20" t="str" cm="1">
         <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>166</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.6">
@@ -9953,11 +10147,11 @@
       </c>
       <c r="E25" s="3" t="str" cm="1">
         <f t="array" ref="E25">IF(COUNTA(E2:E24)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E24)-LEN(SUBSTITUTE(E2:E24,"W","")))/SUMPRODUCT(LEN(E2:E24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (33%)</v>
       </c>
       <c r="F25" s="3" t="str" cm="1">
         <f t="array" ref="F25">IF(COUNTA(F2:F24)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F24)-LEN(SUBSTITUTE(F2:F24,"W","")))/SUMPRODUCT(LEN(F2:F24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (67%)</v>
       </c>
       <c r="G25" s="3" t="str" cm="1">
         <f t="array" ref="G25">IF(COUNTA(G2:G24)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G24)-LEN(SUBSTITUTE(G2:G24,"W","")))/SUMPRODUCT(LEN(G2:G24)),"0%")&amp;")")</f>
@@ -9969,7 +10163,7 @@
       </c>
       <c r="I25" s="1" t="str" cm="1">
         <f t="array" ref="I25">IF(COUNTA(B2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H24)-LEN(SUBSTITUTE(B2:H24,"W","")))/SUMPRODUCT(LEN(B2:H24)),"0%")&amp;")")</f>
-        <v>35 (49%)</v>
+        <v>59 (49%)</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>132</v>
@@ -9977,8 +10171,13 @@
       <c r="K25" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K16">
-    <sortCondition descending="1" ref="I2:I16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="5"/>
+    <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10475,10 +10674,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="78"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11067,10 +11266,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12370,10 +12569,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="70"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13029,10 +13228,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="66"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13733,10 +13932,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14368,10 +14567,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15056,10 +15255,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1048D52B-11E5-4AFB-9C90-5FF958F67FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78B0EF7-0DB8-4DB1-8EB9-32BEF5B086A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="18" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="256">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1002,6 +1002,10 @@
   </si>
   <si>
     <t>6월 14일</t>
+  </si>
+  <si>
+    <t>0613 길탈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1091,7 +1095,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1176,23 +1180,11 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="86">
+  <dxfs count="81">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1214,14 +1206,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFF1A983"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1259,14 +1243,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF8ED973"/>
           <bgColor rgb="FF000000"/>
@@ -1276,31 +1252,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
+          <fgColor rgb="FFBFBFBF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2760,10 +2712,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="84"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="77"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3414,10 +3366,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4108,10 +4060,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="48"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="41"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4823,10 +4775,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5592,10 +5544,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6367,10 +6319,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="29"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7158,10 +7110,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="25"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7929,10 +7881,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8692,10 +8644,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="17"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9463,10 +9415,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9521,7 +9473,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="23" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>47</v>
@@ -9538,20 +9490,24 @@
       <c r="F2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="23" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>47</v>
@@ -9568,14 +9524,18 @@
       <c r="F3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>247</v>
+        <v>162</v>
       </c>
       <c r="K3" s="3"/>
     </row>
@@ -9598,11 +9558,15 @@
       <c r="F4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="G4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>47</v>
+      </c>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>5 (0%)</v>
+        <v>7 (29%)</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>219</v>
@@ -9626,11 +9590,15 @@
       <c r="F5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>4 (0%)</v>
+        <v>6 (0%)</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>241</v>
@@ -9640,164 +9608,176 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (80%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="29" t="str" cm="1">
-        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
-      </c>
-      <c r="J6" s="30" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="17" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A7" s="28" t="s">
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="29" t="str" cm="1">
-        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="18" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
         <v>4 (100%)</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J8" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K8" s="10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="29" t="str" cm="1">
-        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="18" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
         <v>3 (67%)</v>
       </c>
-      <c r="J8" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A9" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="29" t="str" cm="1">
-        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>3 (100%)</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="K9" s="1"/>
+      <c r="J9" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="25" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="I10" s="18" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="7"/>
+        <v>109</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="D11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (100%)</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="K11" s="7"/>
+        <v>168</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="25" t="s">
@@ -9834,11 +9814,15 @@
         <v>48</v>
       </c>
       <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I13" s="19" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>4 (50%)</v>
       </c>
       <c r="J13" s="22" t="s">
         <v>149</v>
@@ -9849,54 +9833,60 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9" t="s">
-        <v>48</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="I14" s="19" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>4 (25%)</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="K14" s="27" t="s">
-        <v>69</v>
+        <v>147</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="H15" s="9"/>
       <c r="I15" s="19" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>41</v>
+        <v>168</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
@@ -9923,98 +9913,108 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="I17" s="20" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>5 (80%)</v>
+        <v>8 (38%)</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>125</v>
+        <v>162</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="26" t="s">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>47</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="G18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (86%)</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>5 (40%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>201</v>
+        <v>189</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
@@ -10151,19 +10151,19 @@
       </c>
       <c r="F25" s="3" t="str" cm="1">
         <f t="array" ref="F25">IF(COUNTA(F2:F24)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F24)-LEN(SUBSTITUTE(F2:F24,"W","")))/SUMPRODUCT(LEN(F2:F24)),"0%")&amp;")")</f>
-        <v>12 (67%)</v>
+        <v>12 (58%)</v>
       </c>
       <c r="G25" s="3" t="str" cm="1">
         <f t="array" ref="G25">IF(COUNTA(G2:G24)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G24)-LEN(SUBSTITUTE(G2:G24,"W","")))/SUMPRODUCT(LEN(G2:G24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (58%)</v>
       </c>
       <c r="H25" s="3" t="str" cm="1">
         <f t="array" ref="H25">IF(COUNTA(H2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H24)-LEN(SUBSTITUTE(H2:H24,"W","")))/SUMPRODUCT(LEN(H2:H24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (50%)</v>
       </c>
       <c r="I25" s="1" t="str" cm="1">
         <f t="array" ref="I25">IF(COUNTA(B2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H24)-LEN(SUBSTITUTE(B2:H24,"W","")))/SUMPRODUCT(LEN(B2:H24)),"0%")&amp;")")</f>
-        <v>59 (49%)</v>
+        <v>83 (49%)</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>132</v>
@@ -10172,11 +10172,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="8"/>
     <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="7"/>
     <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="6"/>
     <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10674,10 +10673,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="80"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="73"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11266,10 +11265,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="69"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12569,10 +12568,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="65"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13228,10 +13227,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="61"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13932,10 +13931,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14567,10 +14566,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15255,10 +15254,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78B0EF7-0DB8-4DB1-8EB9-32BEF5B086A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A91148-F9AE-4842-AEA8-5CDFFA9A94D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="18" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="19" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="5월 5주차" sheetId="23" r:id="rId17"/>
     <sheet name="6월 1주차" sheetId="24" r:id="rId18"/>
     <sheet name="6월 2주차" sheetId="26" r:id="rId19"/>
+    <sheet name="6월 3주차" sheetId="28" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="267">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1005,6 +1006,42 @@
   </si>
   <si>
     <t>0613 길탈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6월 15일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6월 16일</t>
+  </si>
+  <si>
+    <t>6월 17일</t>
+  </si>
+  <si>
+    <t>6월 18일</t>
+  </si>
+  <si>
+    <t>6월 19일</t>
+  </si>
+  <si>
+    <t>6월 20일</t>
+  </si>
+  <si>
+    <t>6월 21일</t>
+  </si>
+  <si>
+    <t>7 (29%)</t>
+  </si>
+  <si>
+    <t>8 (38%)</t>
+  </si>
+  <si>
+    <t>금사향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1095,7 +1132,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1180,11 +1217,26 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
+  <dxfs count="72">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1206,78 +1258,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFF1A983"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2712,10 +2692,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="80"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3366,10 +3346,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="48"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4060,10 +4040,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="44"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4775,10 +4755,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5544,10 +5524,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6319,10 +6299,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7110,10 +7090,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="28"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="12"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7881,10 +7861,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="8"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8644,10 +8624,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9415,10 +9395,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10172,10 +10152,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10673,11 +10653,661 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="60"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75849BA-9334-494A-8CF0-961E5818F918}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="30" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="30" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" s="29"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="30" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="K4" s="31"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="30" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="30" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>2 (100%)</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="30" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="29"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="30" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="30" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="29"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="29"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="30" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>2 (0%)</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="K11" s="29"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" s="29"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="30" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="30" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="20" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="20" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="20" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="20" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="20" t="str" cm="1">
+        <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A22" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="20" t="str" cm="1">
+        <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A23" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="20" t="str" cm="1">
+        <f t="array" ref="I23">IF(COUNTA(B23:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B23:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B23:H23)-LEN(SUBSTITUTE(B23:H23,"W","")))/SUMPRODUCT(LEN(B23:H23)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A24" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="20" t="str" cm="1">
+        <f t="array" ref="I24">IF(COUNTA(B24:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B24:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B24:H24)-LEN(SUBSTITUTE(B24:H24,"W","")))/SUMPRODUCT(LEN(B24:H24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A25" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="3" t="str" cm="1">
+        <f t="array" ref="B25">IF(COUNTA(B2:B24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B24)-LEN(SUBSTITUTE(B2:B24,"W","")))/SUMPRODUCT(LEN(B2:B24)),"0%")&amp;")")</f>
+        <v>12 (25%)</v>
+      </c>
+      <c r="C25" s="3" t="str" cm="1">
+        <f t="array" ref="C25">IF(COUNTA(C2:C24)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C24)-LEN(SUBSTITUTE(C2:C24,"W","")))/SUMPRODUCT(LEN(C2:C24)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="D25" s="3" t="str" cm="1">
+        <f t="array" ref="D25">IF(COUNTA(D2:D24)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D24)-LEN(SUBSTITUTE(D2:D24,"W","")))/SUMPRODUCT(LEN(D2:D24)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="E25" s="3" t="str" cm="1">
+        <f t="array" ref="E25">IF(COUNTA(E2:E24)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E24)-LEN(SUBSTITUTE(E2:E24,"W","")))/SUMPRODUCT(LEN(E2:E24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="F25" s="3" t="str" cm="1">
+        <f t="array" ref="F25">IF(COUNTA(F2:F24)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F24)-LEN(SUBSTITUTE(F2:F24,"W","")))/SUMPRODUCT(LEN(F2:F24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="G25" s="3" t="str" cm="1">
+        <f t="array" ref="G25">IF(COUNTA(G2:G24)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G24)-LEN(SUBSTITUTE(G2:G24,"W","")))/SUMPRODUCT(LEN(G2:G24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="H25" s="3" t="str" cm="1">
+        <f t="array" ref="H25">IF(COUNTA(H2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H24)-LEN(SUBSTITUTE(H2:H24,"W","")))/SUMPRODUCT(LEN(H2:H24)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I25" s="1" t="str" cm="1">
+        <f t="array" ref="I25">IF(COUNTA(B2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H24)-LEN(SUBSTITUTE(B2:H24,"W","")))/SUMPRODUCT(LEN(B2:H24)),"0%")&amp;")")</f>
+        <v>36 (42%)</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K25" s="1"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -11265,10 +11895,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12568,10 +13198,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13227,10 +13857,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13931,10 +14561,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14566,10 +15196,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="56"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15254,10 +15884,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A91148-F9AE-4842-AEA8-5CDFFA9A94D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DA8629-EF5D-472C-A840-52D1077AC6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="19" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="268">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1042,6 +1042,10 @@
   </si>
   <si>
     <t>분수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아픔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1132,7 +1136,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1217,26 +1221,71 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="78">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2692,10 +2741,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="74"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3346,10 +3395,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4040,10 +4089,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="38"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4755,10 +4804,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="34"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5524,10 +5573,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6299,10 +6348,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="26"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7090,10 +7139,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="22"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7861,10 +7910,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8624,10 +8673,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="14"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9395,10 +9444,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10152,10 +10201,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="6"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10653,10 +10702,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="70"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10666,7 +10715,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75849BA-9334-494A-8CF0-961E5818F918}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
@@ -10709,400 +10758,452 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A2" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="30" t="str" cm="1">
+      <c r="A2" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="K2" s="29"/>
+        <v>8 (50%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A3" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="30" t="str" cm="1">
+      <c r="A3" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
-      </c>
-      <c r="J3" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="K3" s="29"/>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="30" t="str" cm="1">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="29" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="K4" s="31"/>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30" t="str" cm="1">
+        <v>121</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="29" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (40%)</v>
-      </c>
-      <c r="J5" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="K5" s="29" t="s">
-        <v>44</v>
-      </c>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30" t="str" cm="1">
+        <v>265</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="29" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>245</v>
-      </c>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="30" t="str" cm="1">
+        <v>55</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="29" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="K7" s="29"/>
+        <v>4 (25%)</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="30" t="str" cm="1">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="29" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>169</v>
-      </c>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="29" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="K9" s="29"/>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30" t="str" cm="1">
+        <v>243</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="29" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>1 (100%)</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="K10" s="29"/>
+        <v>3 (100%)</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="30" t="str" cm="1">
+        <v>266</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="29" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
-      </c>
-      <c r="J11" s="31" t="s">
+        <v>3 (0%)</v>
+      </c>
+      <c r="J11" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="K11" s="29"/>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30" t="str" cm="1">
+        <v>220</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="29" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="K12" s="29"/>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30" t="str" cm="1">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="29" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="K13" s="29" t="s">
-        <v>43</v>
+        <v>2 (0%)</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A14" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30" t="str" cm="1">
+      <c r="A14" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="19" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>41</v>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A15" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="30" t="str" cm="1">
+      <c r="A15" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="19" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>69</v>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A16" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30" t="str" cm="1">
+      <c r="A16" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="20" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>244</v>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="20" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>5 (60%)</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>201</v>
+        <v>143</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="26" t="s">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>48</v>
@@ -11114,43 +11215,39 @@
         <v>47</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>4 (25%)</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>89</v>
@@ -11158,7 +11255,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="26" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -11172,7 +11269,7 @@
         <v>0 (0%)</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>89</v>
@@ -11180,7 +11277,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="26" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -11197,20 +11294,20 @@
         <v>166</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A22" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
       <c r="I22" s="20" t="str" cm="1">
         <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
@@ -11219,20 +11316,20 @@
         <v>166</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A23" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
       <c r="I23" s="20" t="str" cm="1">
         <f t="array" ref="I23">IF(COUNTA(B23:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B23:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B23:H23)-LEN(SUBSTITUTE(B23:H23,"W","")))/SUMPRODUCT(LEN(B23:H23)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
@@ -11241,73 +11338,56 @@
         <v>166</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A24" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="20" t="str" cm="1">
-        <f t="array" ref="I24">IF(COUNTA(B24:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B24:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B24:H24)-LEN(SUBSTITUTE(B24:H24,"W","")))/SUMPRODUCT(LEN(B24:H24)),"0%")&amp;")")</f>
+      <c r="A24" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="3" t="str" cm="1">
+        <f t="array" ref="B24">IF(COUNTA(B2:B23)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B23)-LEN(SUBSTITUTE(B2:B23,"W","")))/SUMPRODUCT(LEN(B2:B23)),"0%")&amp;")")</f>
+        <v>12 (25%)</v>
+      </c>
+      <c r="C24" s="3" t="str" cm="1">
+        <f t="array" ref="C24">IF(COUNTA(C2:C23)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C23)-LEN(SUBSTITUTE(C2:C23,"W","")))/SUMPRODUCT(LEN(C2:C23)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="D24" s="3" t="str" cm="1">
+        <f t="array" ref="D24">IF(COUNTA(D2:D23)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D23)-LEN(SUBSTITUTE(D2:D23,"W","")))/SUMPRODUCT(LEN(D2:D23)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="E24" s="3" t="str" cm="1">
+        <f t="array" ref="E24">IF(COUNTA(E2:E23)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E23)-LEN(SUBSTITUTE(E2:E23,"W","")))/SUMPRODUCT(LEN(E2:E23)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="F24" s="3" t="str" cm="1">
+        <f t="array" ref="F24">IF(COUNTA(F2:F23)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F23)-LEN(SUBSTITUTE(F2:F23,"W","")))/SUMPRODUCT(LEN(F2:F23)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="G24" s="3" t="str" cm="1">
+        <f t="array" ref="G24">IF(COUNTA(G2:G23)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G23)-LEN(SUBSTITUTE(G2:G23,"W","")))/SUMPRODUCT(LEN(G2:G23)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="J24" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A25" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="3" t="str" cm="1">
-        <f t="array" ref="B25">IF(COUNTA(B2:B24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B24)-LEN(SUBSTITUTE(B2:B24,"W","")))/SUMPRODUCT(LEN(B2:B24)),"0%")&amp;")")</f>
-        <v>12 (25%)</v>
-      </c>
-      <c r="C25" s="3" t="str" cm="1">
-        <f t="array" ref="C25">IF(COUNTA(C2:C24)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C24)-LEN(SUBSTITUTE(C2:C24,"W","")))/SUMPRODUCT(LEN(C2:C24)),"0%")&amp;")")</f>
-        <v>12 (58%)</v>
-      </c>
-      <c r="D25" s="3" t="str" cm="1">
-        <f t="array" ref="D25">IF(COUNTA(D2:D24)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D24)-LEN(SUBSTITUTE(D2:D24,"W","")))/SUMPRODUCT(LEN(D2:D24)),"0%")&amp;")")</f>
-        <v>12 (42%)</v>
-      </c>
-      <c r="E25" s="3" t="str" cm="1">
-        <f t="array" ref="E25">IF(COUNTA(E2:E24)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E24)-LEN(SUBSTITUTE(E2:E24,"W","")))/SUMPRODUCT(LEN(E2:E24)),"0%")&amp;")")</f>
+      <c r="H24" s="3" t="str" cm="1">
+        <f t="array" ref="H24">IF(COUNTA(H2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H23)-LEN(SUBSTITUTE(H2:H23,"W","")))/SUMPRODUCT(LEN(H2:H23)),"0%")&amp;")")</f>
         <v>0 (0%)</v>
       </c>
-      <c r="F25" s="3" t="str" cm="1">
-        <f t="array" ref="F25">IF(COUNTA(F2:F24)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F24)-LEN(SUBSTITUTE(F2:F24,"W","")))/SUMPRODUCT(LEN(F2:F24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="G25" s="3" t="str" cm="1">
-        <f t="array" ref="G25">IF(COUNTA(G2:G24)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G24)-LEN(SUBSTITUTE(G2:G24,"W","")))/SUMPRODUCT(LEN(G2:G24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="H25" s="3" t="str" cm="1">
-        <f t="array" ref="H25">IF(COUNTA(H2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H24)-LEN(SUBSTITUTE(H2:H24,"W","")))/SUMPRODUCT(LEN(H2:H24)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="I25" s="1" t="str" cm="1">
-        <f t="array" ref="I25">IF(COUNTA(B2:H24)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H24))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H24)-LEN(SUBSTITUTE(B2:H24,"W","")))/SUMPRODUCT(LEN(B2:H24)),"0%")&amp;")")</f>
-        <v>36 (42%)</v>
-      </c>
-      <c r="J25" s="1" t="s">
+      <c r="I24" s="1" t="str" cm="1">
+        <f t="array" ref="I24">IF(COUNTA(B2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H23)-LEN(SUBSTITUTE(B2:H23,"W","")))/SUMPRODUCT(LEN(B2:H23)),"0%")&amp;")")</f>
+        <v>60 (47%)</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K24" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
+    <sortCondition sortBy="cellColor" ref="I2:I15" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I15" dxfId="4"/>
+    <sortCondition descending="1" ref="I2:I15"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -11895,10 +11975,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="66"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13198,10 +13278,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="62"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13857,10 +13937,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="58"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14561,10 +14641,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15196,10 +15276,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="50"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15884,10 +15964,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DA8629-EF5D-472C-A840-52D1077AC6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D31886-9D4D-4D8F-A09B-8F1570B2AC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="19" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="268">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1237,7 +1237,23 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="82">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -1250,6 +1266,22 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2741,10 +2773,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="78"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3395,10 +3427,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4089,10 +4121,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="42"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4804,10 +4836,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5573,10 +5605,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6348,10 +6380,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="30"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7139,10 +7171,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="24"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="26"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7910,10 +7942,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8673,10 +8705,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="18"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9444,10 +9476,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10201,10 +10233,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="8"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="10"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10702,10 +10734,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="74"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10776,11 +10808,13 @@
       <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>8 (50%)</v>
+        <v>10 (40%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>246</v>
@@ -10808,11 +10842,13 @@
       <c r="F3" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="21" t="s">
+        <v>48</v>
+      </c>
       <c r="H3" s="21"/>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>263</v>
@@ -10820,68 +10856,74 @@
       <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A4" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="29" t="str" cm="1">
+      <c r="A4" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="K4" s="1"/>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A5" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="29" t="str" cm="1">
+      <c r="A5" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -10889,9 +10931,7 @@
       <c r="E6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="29" t="str" cm="1">
@@ -10899,7 +10939,7 @@
         <v>4 (50%)</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="K6" s="1"/>
     </row>
@@ -10933,97 +10973,101 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="29" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>4 (25%)</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="28" t="s">
-        <v>7</v>
+        <v>243</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="29" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>4 (100%)</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>69</v>
+        <v>163</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="29" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>3 (100%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>48</v>
@@ -11032,37 +11076,39 @@
       <c r="H11" s="1"/>
       <c r="I11" s="29" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>3 (0%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J11" s="30" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="29" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>43</v>
+        <v>148</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
@@ -11078,11 +11124,13 @@
         <v>48</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="29" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J13" s="30" t="s">
         <v>152</v>
@@ -11139,66 +11187,70 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="5"/>
       <c r="I16" s="20" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (67%)</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>201</v>
+        <v>143</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="12"/>
       <c r="I17" s="20" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>125</v>
+        <v>264</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
@@ -11218,11 +11270,13 @@
       <c r="F18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="I18" s="20" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
+        <v>5 (40%)</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>162</v>
@@ -11367,7 +11421,7 @@
       </c>
       <c r="G24" s="3" t="str" cm="1">
         <f t="array" ref="G24">IF(COUNTA(G2:G23)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G23)-LEN(SUBSTITUTE(G2:G23,"W","")))/SUMPRODUCT(LEN(G2:G23)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (58%)</v>
       </c>
       <c r="H24" s="3" t="str" cm="1">
         <f t="array" ref="H24">IF(COUNTA(H2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H23)-LEN(SUBSTITUTE(H2:H23,"W","")))/SUMPRODUCT(LEN(H2:H23)),"0%")&amp;")")</f>
@@ -11375,7 +11429,7 @@
       </c>
       <c r="I24" s="1" t="str" cm="1">
         <f t="array" ref="I24">IF(COUNTA(B2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H23)-LEN(SUBSTITUTE(B2:H23,"W","")))/SUMPRODUCT(LEN(B2:H23)),"0%")&amp;")")</f>
-        <v>60 (47%)</v>
+        <v>72 (49%)</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>132</v>
@@ -11383,10 +11437,12 @@
       <c r="K24" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
-    <sortCondition sortBy="cellColor" ref="I2:I15" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I15" dxfId="4"/>
-    <sortCondition descending="1" ref="I2:I15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="4"/>
+    <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11975,10 +12031,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="70"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13278,10 +13334,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="66"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13937,10 +13993,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="62"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14641,10 +14697,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15276,10 +15332,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15964,10 +16020,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D31886-9D4D-4D8F-A09B-8F1570B2AC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4CBDAF-ACF5-43D3-ACFC-555FC6F7D2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="13" activeTab="19" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="4507" yWindow="698" windowWidth="14220" windowHeight="12082" firstSheet="16" activeTab="19" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="268">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1136,7 +1136,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1221,23 +1221,11 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="82">
+  <dxfs count="84">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1256,9 +1244,9 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1288,9 +1276,9 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1298,6 +1286,22 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2773,10 +2777,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="82"/>
     <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="81"/>
     <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="80"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="78"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3427,10 +3431,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="48"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4121,10 +4125,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="46"/>
     <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="45"/>
     <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="44"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="42"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4836,10 +4840,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
     <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
     <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5605,10 +5609,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6380,10 +6384,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7171,10 +7175,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
     <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="29"/>
     <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="28"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="26"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7942,10 +7946,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8705,10 +8709,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9476,10 +9480,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
     <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10233,10 +10237,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="14"/>
     <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="13"/>
     <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="12"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="10"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10734,10 +10738,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="78"/>
     <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="77"/>
     <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="74"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10811,10 +10815,12 @@
       <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>10 (40%)</v>
+        <v>12 (42%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>246</v>
@@ -10845,10 +10851,12 @@
       <c r="G3" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="21"/>
+      <c r="H3" s="21" t="s">
+        <v>47</v>
+      </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>6 (50%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>263</v>
@@ -10875,10 +10883,12 @@
       <c r="G4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>147</v>
@@ -10905,10 +10915,12 @@
       <c r="G5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (40%)</v>
+        <v>6 (33%)</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>166</v>
@@ -10916,226 +10928,234 @@
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="17" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="29" t="str" cm="1">
-        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+      <c r="B8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="18" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
         <v>4 (50%)</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J8" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A7" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="29" t="str" cm="1">
-        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="18" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
         <v>4 (25%)</v>
       </c>
-      <c r="J7" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="29" t="str" cm="1">
-        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A9" s="28" t="s">
+      <c r="J9" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="29" t="str" cm="1">
-        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+      <c r="B10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="18" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
         <v>4 (100%)</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="J10" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A10" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="29" t="str" cm="1">
-        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="29" t="str" cm="1">
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
         <v>3 (33%)</v>
       </c>
-      <c r="J11" s="30" t="s">
+      <c r="J11" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A12" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="29" t="str" cm="1">
+      <c r="A12" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="19" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="K12" s="31" t="s">
-        <v>69</v>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="29" t="str" cm="1">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="19" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
-      </c>
-      <c r="J13" s="30" t="s">
+        <v>4 (50%)</v>
+      </c>
+      <c r="J13" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="9" t="s">
         <v>41</v>
       </c>
     </row>
@@ -11207,10 +11227,12 @@
       <c r="G16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="I16" s="20" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J16" s="12" t="s">
         <v>143</v>
@@ -11241,10 +11263,12 @@
       <c r="G17" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="12"/>
+      <c r="H17" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="I17" s="20" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>6 (50%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J17" s="12" t="s">
         <v>264</v>
@@ -11425,11 +11449,11 @@
       </c>
       <c r="H24" s="3" t="str" cm="1">
         <f t="array" ref="H24">IF(COUNTA(H2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H23)-LEN(SUBSTITUTE(H2:H23,"W","")))/SUMPRODUCT(LEN(H2:H23)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (25%)</v>
       </c>
       <c r="I24" s="1" t="str" cm="1">
         <f t="array" ref="I24">IF(COUNTA(B2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H23)-LEN(SUBSTITUTE(B2:H23,"W","")))/SUMPRODUCT(LEN(B2:H23)),"0%")&amp;")")</f>
-        <v>72 (49%)</v>
+        <v>84 (45%)</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>132</v>
@@ -12031,10 +12055,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
     <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="73"/>
     <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="70"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13334,10 +13358,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="70"/>
     <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="69"/>
     <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="66"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13993,10 +14017,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="66"/>
     <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="65"/>
     <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="62"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14697,10 +14721,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
     <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="61"/>
     <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15332,10 +15356,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
     <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="57"/>
     <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="56"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16020,10 +16044,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
     <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="53"/>
     <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="52"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4CBDAF-ACF5-43D3-ACFC-555FC6F7D2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDCA6AAB-70BD-4BA8-BDDC-25490EBAE9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4507" yWindow="698" windowWidth="14220" windowHeight="12082" firstSheet="16" activeTab="19" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="20" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="6월 1주차" sheetId="24" r:id="rId18"/>
     <sheet name="6월 2주차" sheetId="26" r:id="rId19"/>
     <sheet name="6월 3주차" sheetId="28" r:id="rId20"/>
+    <sheet name="6월 4주차" sheetId="29" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -81,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="276">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1047,6 +1048,31 @@
   <si>
     <t>아픔</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12 (42%)</t>
+  </si>
+  <si>
+    <t>6월 22일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6월 23일</t>
+  </si>
+  <si>
+    <t>6월 24일</t>
+  </si>
+  <si>
+    <t>6월 25일</t>
+  </si>
+  <si>
+    <t>6월 26일</t>
+  </si>
+  <si>
+    <t>6월 27일</t>
+  </si>
+  <si>
+    <t>6월 28일</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1251,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="84">
+  <dxfs count="76">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1247,70 +1273,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFF1A983"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2777,10 +2739,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3431,10 +3393,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4125,10 +4087,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4840,10 +4802,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5609,10 +5571,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6384,10 +6346,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7175,10 +7137,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7946,10 +7908,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8709,10 +8671,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="8"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9480,10 +9442,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10237,10 +10199,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10738,10 +10700,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="64"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11462,12 +11424,712 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="72"/>
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E38216E-C9EA-4820-9C82-FA16AC4E8359}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>7 (57%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="21"/>
+      <c r="I3" s="17" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>6 (33%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="21"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>5 (80%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>6 (17%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="17" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="18" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="18" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="18" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="18" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="19" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>4 (75%)</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="19" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="19" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="19" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="20" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>6 (50%)</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="20" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>6 (67%)</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="20" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="20" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="20" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="20" t="str" cm="1">
+        <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A22" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="20" t="str" cm="1">
+        <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A23" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="20" t="str" cm="1">
+        <f t="array" ref="I23">IF(COUNTA(B23:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B23:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B23:H23)-LEN(SUBSTITUTE(B23:H23,"W","")))/SUMPRODUCT(LEN(B23:H23)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A24" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="3" t="str" cm="1">
+        <f t="array" ref="B24">IF(COUNTA(B2:B23)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B23)-LEN(SUBSTITUTE(B2:B23,"W","")))/SUMPRODUCT(LEN(B2:B23)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="C24" s="3" t="str" cm="1">
+        <f t="array" ref="C24">IF(COUNTA(C2:C23)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C23)-LEN(SUBSTITUTE(C2:C23,"W","")))/SUMPRODUCT(LEN(C2:C23)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="D24" s="3" t="str" cm="1">
+        <f t="array" ref="D24">IF(COUNTA(D2:D23)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D23)-LEN(SUBSTITUTE(D2:D23,"W","")))/SUMPRODUCT(LEN(D2:D23)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="E24" s="3" t="str" cm="1">
+        <f t="array" ref="E24">IF(COUNTA(E2:E23)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E23)-LEN(SUBSTITUTE(E2:E23,"W","")))/SUMPRODUCT(LEN(E2:E23)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="F24" s="3" t="str" cm="1">
+        <f t="array" ref="F24">IF(COUNTA(F2:F23)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F23)-LEN(SUBSTITUTE(F2:F23,"W","")))/SUMPRODUCT(LEN(F2:F23)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="G24" s="3" t="str" cm="1">
+        <f t="array" ref="G24">IF(COUNTA(G2:G23)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G23)-LEN(SUBSTITUTE(G2:G23,"W","")))/SUMPRODUCT(LEN(G2:G23)),"0%")&amp;")")</f>
+        <v>12 (25%)</v>
+      </c>
+      <c r="H24" s="3" t="str" cm="1">
+        <f t="array" ref="H24">IF(COUNTA(H2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H23)-LEN(SUBSTITUTE(H2:H23,"W","")))/SUMPRODUCT(LEN(H2:H23)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I24" s="1" t="str" cm="1">
+        <f t="array" ref="I24">IF(COUNTA(B2:H23)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H23))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H23)-LEN(SUBSTITUTE(B2:H23,"W","")))/SUMPRODUCT(LEN(B2:H23)),"0%")&amp;")")</f>
+        <v>72 (50%)</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K24" s="1"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -12055,10 +12717,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13358,10 +14020,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14017,10 +14679,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14721,10 +15383,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15356,10 +16018,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16044,10 +16706,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDCA6AAB-70BD-4BA8-BDDC-25490EBAE9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19BEF94-82FD-40F2-85D7-4BB090F10A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="20" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="21" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="6월 2주차" sheetId="26" r:id="rId19"/>
     <sheet name="6월 3주차" sheetId="28" r:id="rId20"/>
     <sheet name="6월 4주차" sheetId="29" r:id="rId21"/>
+    <sheet name="7월 3주차" sheetId="30" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="291">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1073,6 +1074,60 @@
   </si>
   <si>
     <t>6월 28일</t>
+  </si>
+  <si>
+    <t>뭉치핑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재범</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캄척</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 6일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 7일</t>
+  </si>
+  <si>
+    <t>7월 8일</t>
+  </si>
+  <si>
+    <t>7월 9일</t>
+  </si>
+  <si>
+    <t>7월 10일</t>
+  </si>
+  <si>
+    <t>7월 11일</t>
+  </si>
+  <si>
+    <t>7월 12일</t>
+  </si>
+  <si>
+    <t>도윤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 (0%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가입 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1162,7 +1217,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1247,11 +1302,250 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="76">
+  <dxfs count="104">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2739,10 +3033,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="103"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="102"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="101"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="100"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3393,10 +3687,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4087,10 +4381,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4802,10 +5096,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5571,10 +5865,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6346,10 +6640,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7137,10 +7431,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7908,10 +8202,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8671,10 +8965,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9442,10 +9736,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10199,10 +10493,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10700,10 +10994,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="99"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="98"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="97"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="96"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11424,10 +11718,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="28"/>
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12136,6 +12430,625 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60632166-B613-48F8-80E3-192361B952B6}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>12 (83%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="17" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>6 (50%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>6 (50%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="30" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="K7" s="29"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="30" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="K8" s="29"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="19" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>4 (25%)</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="19" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="19" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="18" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="18" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>3 (100%)</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="18" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>2 (100%)</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="18" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="18" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="20" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>6 (67%)</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="20" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>4 (75%)</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="20" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="20" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3" t="str" cm="1">
+        <f t="array" ref="B21">IF(COUNTA(B2:B20)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B20)-LEN(SUBSTITUTE(B2:B20,"W","")))/SUMPRODUCT(LEN(B2:B20)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="C21" s="3" t="str" cm="1">
+        <f t="array" ref="C21">IF(COUNTA(C2:C20)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C20)-LEN(SUBSTITUTE(C2:C20,"W","")))/SUMPRODUCT(LEN(C2:C20)),"0%")&amp;")")</f>
+        <v>12 (83%)</v>
+      </c>
+      <c r="D21" s="3" t="str" cm="1">
+        <f t="array" ref="D21">IF(COUNTA(D2:D20)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D20)-LEN(SUBSTITUTE(D2:D20,"W","")))/SUMPRODUCT(LEN(D2:D20)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="E21" s="7" t="str" cm="1">
+        <f t="array" ref="E21">IF(COUNTA(E2:E20)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E20)-LEN(SUBSTITUTE(E2:E20,"W","")))/SUMPRODUCT(LEN(E2:E20)),"0%")&amp;")")</f>
+        <v>11 (55%)</v>
+      </c>
+      <c r="F21" s="3" t="str" cm="1">
+        <f t="array" ref="F21">IF(COUNTA(F2:F20)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F20)-LEN(SUBSTITUTE(F2:F20,"W","")))/SUMPRODUCT(LEN(F2:F20)),"0%")&amp;")")</f>
+        <v>12 (75%)</v>
+      </c>
+      <c r="G21" s="3" t="str" cm="1">
+        <f t="array" ref="G21">IF(COUNTA(G2:G20)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G20)-LEN(SUBSTITUTE(G2:G20,"W","")))/SUMPRODUCT(LEN(G2:G20)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="H21" s="29" t="str" cm="1">
+        <f t="array" ref="H21">IF(COUNTA(H2:H20)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H20)-LEN(SUBSTITUTE(H2:H20,"W","")))/SUMPRODUCT(LEN(H2:H20)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I21" s="1" t="str" cm="1">
+        <f t="array" ref="I21">IF(COUNTA(B2:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H20)-LEN(SUBSTITUTE(B2:H20,"W","")))/SUMPRODUCT(LEN(B2:H20)),"0%")&amp;")")</f>
+        <v>71 (62%)</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K20">
+    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="5"/>
+    <sortCondition descending="1" ref="I3:I20"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50CE732-75BA-447A-8460-A6EB1DB46D96}">
   <dimension ref="A1:L25"/>
@@ -12717,10 +13630,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="95"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="94"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="93"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="92"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14020,10 +14933,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="88"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14679,10 +15592,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="84"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15383,10 +16296,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="80"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16018,10 +16931,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="76"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16706,10 +17619,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="72"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19BEF94-82FD-40F2-85D7-4BB090F10A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C872F32-56E3-4090-ACAA-47E62ADBFFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="21" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="291">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1217,7 +1217,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1302,26 +1302,11 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="104">
+  <dxfs count="80">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1348,200 +1333,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3033,10 +2826,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="103"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="102"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="101"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="100"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="76"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3687,10 +3480,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4381,10 +4174,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5096,10 +4889,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5865,10 +5658,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6640,10 +6433,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7431,10 +7224,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8202,10 +7995,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8965,10 +8758,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9736,10 +9529,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10493,10 +10286,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="8"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10994,10 +10787,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="99"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="98"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="97"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="96"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="72"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11718,10 +11511,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="4"/>
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12461,7 +12254,7 @@
       <c r="G1" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="13" t="s">
         <v>286</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -12496,10 +12289,12 @@
       <c r="G2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>12 (83%)</v>
+        <v>14 (71%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>289</v>
@@ -12510,7 +12305,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="23" t="s">
-        <v>277</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>48</v>
@@ -12522,18 +12317,20 @@
         <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>47</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>6 (50%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>166</v>
@@ -12542,7 +12339,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="23" t="s">
-        <v>2</v>
+        <v>277</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>48</v>
@@ -12554,18 +12351,20 @@
         <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>6 (50%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>166</v>
@@ -12592,10 +12391,12 @@
       <c r="G5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>166</v>
@@ -12622,10 +12423,12 @@
       <c r="G6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I6" s="17" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>5 (40%)</v>
+        <v>6 (33%)</v>
       </c>
       <c r="J6" s="21" t="s">
         <v>166</v>
@@ -12633,164 +12436,168 @@
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="30" t="str" cm="1">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="17" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
-      </c>
-      <c r="J7" s="31" t="s">
+        <v>5 (40%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="K7" s="29"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="30" t="str" cm="1">
+      <c r="A8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="19" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
-      </c>
-      <c r="J8" s="31" t="s">
+        <v>4 (25%)</v>
+      </c>
+      <c r="J8" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="29"/>
+      <c r="K8" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="G9" s="9" t="s">
         <v>48</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="19" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>4 (25%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J9" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="27" t="s">
-        <v>69</v>
+      <c r="K9" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="24" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="19" t="str" cm="1">
         <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J10" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>41</v>
-      </c>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A11" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="19" t="str" cm="1">
+      <c r="A11" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J11" s="22" t="s">
+        <v>4 (75%)</v>
+      </c>
+      <c r="J11" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="K11" s="9"/>
+      <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
+        <v>55</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="18" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>4 (50%)</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="K12" s="16"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="25" t="s">
@@ -12832,10 +12639,12 @@
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="I14" s="18" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
+        <v>3 (100%)</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>166</v>
@@ -12844,20 +12653,20 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="25" t="s">
-        <v>12</v>
+        <v>276</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="I15" s="18" t="str" cm="1">
         <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
+        <v>1 (100%)</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>166</v>
@@ -12866,18 +12675,20 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="25" t="s">
-        <v>276</v>
+        <v>12</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="F16" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="18" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>1 (0%)</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>166</v>
@@ -12906,10 +12717,12 @@
       <c r="G17" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="12"/>
+      <c r="H17" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="I17" s="20" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J17" s="12" t="s">
         <v>166</v>
@@ -12958,10 +12771,12 @@
       <c r="G19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
+        <v>3 (67%)</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>166</v>
@@ -13022,13 +12837,13 @@
         <f t="array" ref="G21">IF(COUNTA(G2:G20)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G20)-LEN(SUBSTITUTE(G2:G20,"W","")))/SUMPRODUCT(LEN(G2:G20)),"0%")&amp;")")</f>
         <v>12 (50%)</v>
       </c>
-      <c r="H21" s="29" t="str" cm="1">
+      <c r="H21" s="3" t="str" cm="1">
         <f t="array" ref="H21">IF(COUNTA(H2:H20)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H20)-LEN(SUBSTITUTE(H2:H20,"W","")))/SUMPRODUCT(LEN(H2:H20)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (42%)</v>
       </c>
       <c r="I21" s="1" t="str" cm="1">
         <f t="array" ref="I21">IF(COUNTA(B2:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H20)-LEN(SUBSTITUTE(B2:H20,"W","")))/SUMPRODUCT(LEN(B2:H20)),"0%")&amp;")")</f>
-        <v>71 (62%)</v>
+        <v>83 (59%)</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>132</v>
@@ -13036,13 +12851,12 @@
       <c r="K21" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K20">
-    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="8"/>
-    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I3:I20" dxfId="5"/>
-    <sortCondition descending="1" ref="I3:I20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K21">
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="0"/>
+    <sortCondition descending="1" ref="I3:I21"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13630,10 +13444,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="95"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="94"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="93"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="92"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14933,10 +14747,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="91"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="90"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15592,10 +15406,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="87"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="86"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16296,10 +16110,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16931,10 +16745,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -17619,10 +17433,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C872F32-56E3-4090-ACAA-47E62ADBFFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C225D7A-9118-4BA6-9255-AAF992CDB30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="21" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="22" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="6월 3주차" sheetId="28" r:id="rId20"/>
     <sheet name="6월 4주차" sheetId="29" r:id="rId21"/>
     <sheet name="7월 3주차" sheetId="30" r:id="rId22"/>
+    <sheet name="7월 4주차" sheetId="31" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="301">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1127,6 +1128,39 @@
   </si>
   <si>
     <t>가입 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14 (71%)</t>
+  </si>
+  <si>
+    <t>7월 13일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 14일</t>
+  </si>
+  <si>
+    <t>7월 15일</t>
+  </si>
+  <si>
+    <t>7월 16일</t>
+  </si>
+  <si>
+    <t>7월 17일</t>
+  </si>
+  <si>
+    <t>7월 18일</t>
+  </si>
+  <si>
+    <t>7월 19일</t>
+  </si>
+  <si>
+    <t>뽀로로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INFORA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1306,7 +1340,103 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="80">
+  <dxfs count="96">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1947,6 +2077,38 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2826,10 +2988,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="88"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3480,10 +3642,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4174,10 +4336,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4889,10 +5051,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5658,10 +5820,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6433,10 +6595,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7224,10 +7386,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7995,10 +8157,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8758,10 +8920,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9529,10 +9691,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10286,10 +10448,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10787,10 +10949,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="84"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11511,10 +11673,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="16"/>
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12852,11 +13014,667 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K21">
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="95"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="94"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="93"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="92"/>
     <sortCondition descending="1" ref="I3:I21"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA75011-282E-420B-A9CE-9BB86C4D912E}">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>6 (67%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="17" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="19" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="19" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>2 (100%)</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="19" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="19" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="18" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>4 (75%)</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="18" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>4 (0%)</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="18" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="18" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>3 (0%)</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="18" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="18" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="18" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>2 (0%)</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="18" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="20" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="20" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
+        <v>4 (100%)</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="20" t="str" cm="1">
+        <f t="array" ref="I21">IF(COUNTA(B21:H21)=0,"0 (0%)",SUMPRODUCT(LEN(B21:H21))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B21:H21)-LEN(SUBSTITUTE(B21:H21,"W","")))/SUMPRODUCT(LEN(B21:H21)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A22" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="20" t="str" cm="1">
+        <f t="array" ref="I22">IF(COUNTA(B22:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B22:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B22:H22)-LEN(SUBSTITUTE(B22:H22,"W","")))/SUMPRODUCT(LEN(B22:H22)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A23" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="3" t="str" cm="1">
+        <f t="array" ref="B23">IF(COUNTA(B2:B22)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B22)-LEN(SUBSTITUTE(B2:B22,"W","")))/SUMPRODUCT(LEN(B2:B22)),"0%")&amp;")")</f>
+        <v>12 (33%)</v>
+      </c>
+      <c r="C23" s="3" t="str" cm="1">
+        <f t="array" ref="C23">IF(COUNTA(C2:C22)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C22)-LEN(SUBSTITUTE(C2:C22,"W","")))/SUMPRODUCT(LEN(C2:C22)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="D23" s="3" t="str" cm="1">
+        <f t="array" ref="D23">IF(COUNTA(D2:D22)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D22)-LEN(SUBSTITUTE(D2:D22,"W","")))/SUMPRODUCT(LEN(D2:D22)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="E23" s="3" t="str" cm="1">
+        <f t="array" ref="E23">IF(COUNTA(E2:E22)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E22)-LEN(SUBSTITUTE(E2:E22,"W","")))/SUMPRODUCT(LEN(E2:E22)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="F23" s="3" t="str" cm="1">
+        <f t="array" ref="F23">IF(COUNTA(F2:F22)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F22)-LEN(SUBSTITUTE(F2:F22,"W","")))/SUMPRODUCT(LEN(F2:F22)),"0%")&amp;")")</f>
+        <v>12 (75%)</v>
+      </c>
+      <c r="G23" s="3" t="str" cm="1">
+        <f t="array" ref="G23">IF(COUNTA(G2:G22)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G22)-LEN(SUBSTITUTE(G2:G22,"W","")))/SUMPRODUCT(LEN(G2:G22)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="H23" s="3" t="str" cm="1">
+        <f t="array" ref="H23">IF(COUNTA(H2:H22)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H22)-LEN(SUBSTITUTE(H2:H22,"W","")))/SUMPRODUCT(LEN(H2:H22)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I23" s="1" t="str" cm="1">
+        <f t="array" ref="I23">IF(COUNTA(B2:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H22)-LEN(SUBSTITUTE(B2:H22,"W","")))/SUMPRODUCT(LEN(B2:H22)),"0%")&amp;")")</f>
+        <v>60 (55%)</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K23" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="4"/>
+    <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13444,10 +14262,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="80"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14747,10 +15565,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="76"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15406,10 +16224,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="72"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16110,10 +16928,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16745,10 +17563,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -17433,10 +18251,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C225D7A-9118-4BA6-9255-AAF992CDB30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52030DB-7C54-4CC5-8AEE-7552D05D5A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="22" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="301">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1340,7 +1340,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="96">
+  <dxfs count="92">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2077,38 +2077,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -13014,10 +12982,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K21">
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="95"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="94"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="93"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="92"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="12"/>
     <sortCondition descending="1" ref="I3:I21"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13088,11 +13056,15 @@
       <c r="F2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>8 (50%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>291</v>
@@ -13103,13 +13075,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="23" t="s">
-        <v>2</v>
+        <v>277</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>47</v>
@@ -13118,25 +13090,29 @@
         <v>47</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="23" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>48</v>
@@ -13145,49 +13121,57 @@
         <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="23" t="s">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -13210,11 +13194,15 @@
       <c r="F6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I6" s="17" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J6" s="21" t="s">
         <v>183</v>
@@ -13222,210 +13210,234 @@
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="17" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>6 (83%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="K7" s="21"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="17" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="17" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="17" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>5 (0%)</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="19" t="str" cm="1">
-        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>2 (50%)</v>
-      </c>
-      <c r="J7" s="22" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="19" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K11" s="9" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="19" t="str" cm="1">
-        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>2 (100%)</v>
-      </c>
-      <c r="J8" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A9" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="19" t="str" cm="1">
-        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>1 (0%)</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A10" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="19" t="str" cm="1">
-        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A11" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="18" t="str" cm="1">
-        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>4 (75%)</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" s="25" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H12" s="7"/>
       <c r="I12" s="18" t="str" cm="1">
         <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
-        <v>4 (0%)</v>
+        <v>3 (33%)</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="25" t="s">
-        <v>287</v>
+        <v>7</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="7"/>
+        <v>47</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>3 (67%)</v>
+        <v>3 (100%)</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="K13" s="7"/>
+        <v>152</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>48</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H14" s="7"/>
       <c r="I14" s="18" t="str" cm="1">
         <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
-        <v>3 (0%)</v>
+        <v>2 (50%)</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="K14" s="7"/>
+        <v>150</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="25" t="s">
@@ -13449,7 +13461,9 @@
       <c r="J15" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="K15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="25" t="s">
@@ -13474,32 +13488,30 @@
         <v>166</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>48</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="18" t="str" cm="1">
         <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
-        <v>2 (0%)</v>
+        <v>0 (0%)</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="K17" s="7"/>
+        <v>166</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="25" t="s">
@@ -13519,7 +13531,9 @@
       <c r="J18" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="K18" s="7"/>
+      <c r="K18" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="26" t="s">
@@ -13540,11 +13554,15 @@
       <c r="F19" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="I19" s="20" t="str" cm="1">
         <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>7 (71%)</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>144</v>
@@ -13570,11 +13588,13 @@
       <c r="F20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H20" s="5"/>
       <c r="I20" s="20" t="str" cm="1">
         <f t="array" ref="I20">IF(COUNTA(B20:H20)=0,"0 (0%)",SUMPRODUCT(LEN(B20:H20))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B20:H20)-LEN(SUBSTITUTE(B20:H20,"W","")))/SUMPRODUCT(LEN(B20:H20)),"0%")&amp;")")</f>
-        <v>4 (100%)</v>
+        <v>5 (100%)</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>150</v>
@@ -13653,15 +13673,15 @@
       </c>
       <c r="G23" s="3" t="str" cm="1">
         <f t="array" ref="G23">IF(COUNTA(G2:G22)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G22)-LEN(SUBSTITUTE(G2:G22,"W","")))/SUMPRODUCT(LEN(G2:G22)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (58%)</v>
       </c>
       <c r="H23" s="3" t="str" cm="1">
         <f t="array" ref="H23">IF(COUNTA(H2:H22)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H22)-LEN(SUBSTITUTE(H2:H22,"W","")))/SUMPRODUCT(LEN(H2:H22)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
+        <v>12 (33%)</v>
       </c>
       <c r="I23" s="1" t="str" cm="1">
         <f t="array" ref="I23">IF(COUNTA(B2:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H22)-LEN(SUBSTITUTE(B2:H22,"W","")))/SUMPRODUCT(LEN(B2:H22)),"0%")&amp;")")</f>
-        <v>60 (55%)</v>
+        <v>84 (52%)</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>132</v>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52030DB-7C54-4CC5-8AEE-7552D05D5A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063FA7B2-873D-4DB2-9101-B3F48B5F230E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="22" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="17" activeTab="23" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="6월 4주차" sheetId="29" r:id="rId21"/>
     <sheet name="7월 3주차" sheetId="30" r:id="rId22"/>
     <sheet name="7월 4주차" sheetId="31" r:id="rId23"/>
+    <sheet name="7월 5주차" sheetId="32" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -84,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="309">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1161,6 +1162,32 @@
   </si>
   <si>
     <t>INFORA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 20일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 21일</t>
+  </si>
+  <si>
+    <t>7월 22일</t>
+  </si>
+  <si>
+    <t>7월 23일</t>
+  </si>
+  <si>
+    <t>7월 24일</t>
+  </si>
+  <si>
+    <t>7월 25일</t>
+  </si>
+  <si>
+    <t>7월 26일</t>
+  </si>
+  <si>
+    <t>3번 + 명성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1340,7 +1367,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="92">
+  <dxfs count="104">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1424,7 +1451,71 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2077,6 +2168,38 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2956,10 +3079,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="91"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="90"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="99"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="98"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="97"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="96"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3610,10 +3733,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4304,10 +4427,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5019,10 +5142,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="49"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5788,10 +5911,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6563,10 +6686,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7354,10 +7477,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8125,10 +8248,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8888,10 +9011,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9659,10 +9782,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10416,10 +10539,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10917,10 +11040,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="87"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="86"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="95"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="94"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="93"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="92"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11641,10 +11764,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="24"/>
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12982,10 +13105,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K21">
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="20"/>
     <sortCondition descending="1" ref="I3:I21"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13690,11 +13813,577 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="103"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="102"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="101"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="100"/>
     <sortCondition descending="1" ref="I2:I22"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC55A5B1-F09B-42CA-9FF0-F003FB9D3FD5}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="17" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>7 (57%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="17" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>6 (67%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>6 (50%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="17" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="17" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="17" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>5 (100%)</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="19" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="18" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="18" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="18" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="18" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>2 (50%)</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="18" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="20" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>8 (50%)</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="20" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="3" t="str" cm="1">
+        <f t="array" ref="B18">IF(COUNTA(B2:B17)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B17)-LEN(SUBSTITUTE(B2:B17,"W","")))/SUMPRODUCT(LEN(B2:B17)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="C18" s="3" t="str" cm="1">
+        <f t="array" ref="C18">IF(COUNTA(C2:C17)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C17)-LEN(SUBSTITUTE(C2:C17,"W","")))/SUMPRODUCT(LEN(C2:C17)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="D18" s="3" t="str" cm="1">
+        <f t="array" ref="D18">IF(COUNTA(D2:D17)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D17)-LEN(SUBSTITUTE(D2:D17,"W","")))/SUMPRODUCT(LEN(D2:D17)),"0%")&amp;")")</f>
+        <v>12 (33%)</v>
+      </c>
+      <c r="E18" s="3" t="str" cm="1">
+        <f t="array" ref="E18">IF(COUNTA(E2:E17)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E17)-LEN(SUBSTITUTE(E2:E17,"W","")))/SUMPRODUCT(LEN(E2:E17)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="F18" s="3" t="str" cm="1">
+        <f t="array" ref="F18">IF(COUNTA(F2:F17)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F17)-LEN(SUBSTITUTE(F2:F17,"W","")))/SUMPRODUCT(LEN(F2:F17)),"0%")&amp;")")</f>
+        <v>12 (75%)</v>
+      </c>
+      <c r="G18" s="3" t="str" cm="1">
+        <f t="array" ref="G18">IF(COUNTA(G2:G17)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G17)-LEN(SUBSTITUTE(G2:G17,"W","")))/SUMPRODUCT(LEN(G2:G17)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="H18" s="3" t="str" cm="1">
+        <f t="array" ref="H18">IF(COUNTA(H2:H17)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H17)-LEN(SUBSTITUTE(H2:H17,"W","")))/SUMPRODUCT(LEN(H2:H17)),"0%")&amp;")")</f>
+        <v>0 (0%)</v>
+      </c>
+      <c r="I18" s="1" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B2:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H17)-LEN(SUBSTITUTE(B2:H17,"W","")))/SUMPRODUCT(LEN(B2:H17)),"0%")&amp;")")</f>
+        <v>72 (54%)</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="4"/>
+    <sortCondition descending="1" ref="I2:I17"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14282,10 +14971,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="88"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15585,10 +16274,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="84"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16244,10 +16933,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="80"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16948,10 +17637,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="76"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -17583,10 +18272,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="72"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18271,10 +18960,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063FA7B2-873D-4DB2-9101-B3F48B5F230E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB24936A-EC29-4FD5-8E51-8B37159B6247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="17" activeTab="23" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="19" activeTab="24" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="7월 3주차" sheetId="30" r:id="rId22"/>
     <sheet name="7월 4주차" sheetId="31" r:id="rId23"/>
     <sheet name="7월 5주차" sheetId="32" r:id="rId24"/>
+    <sheet name="8월 1주차" sheetId="33" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2월 3주차'!$A$2:$I$8</definedName>
@@ -85,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2911" uniqueCount="320">
   <si>
     <t>밋</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1188,6 +1189,42 @@
   </si>
   <si>
     <t>3번 + 명성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 27일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월 28일</t>
+  </si>
+  <si>
+    <t>7월 29일</t>
+  </si>
+  <si>
+    <t>7월 30일</t>
+  </si>
+  <si>
+    <t>7월 31일</t>
+  </si>
+  <si>
+    <t>8월 1일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8월 2일</t>
+  </si>
+  <si>
+    <t>6 (17%)</t>
+  </si>
+  <si>
+    <t>6 (100%)</t>
+  </si>
+  <si>
+    <t>9 (44%)</t>
+  </si>
+  <si>
+    <t>예다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1367,7 +1404,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="104">
+  <dxfs count="146">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1451,23 +1488,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1499,6 +1520,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF8ED973"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1516,6 +1545,316 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED973"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1A983"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3079,10 +3418,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="99"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="98"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="97"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="96"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="141"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="140"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="139"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="138"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3733,10 +4072,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="66"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="109"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="108"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="107"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="106"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4427,10 +4766,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="62"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="105"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="104"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="103"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="102"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5142,10 +5481,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="58"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="57"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="56"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="101"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="100"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="99"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="98"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5911,10 +6250,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="55"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="54"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="97"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="96"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="95"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="94"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6686,10 +7025,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="51"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="50"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="49"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="48"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="93"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="92"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="91"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="90"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7477,10 +7816,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="47"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="46"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="45"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="86"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8248,10 +8587,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="82"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9011,10 +9350,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="36"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="78"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9782,10 +10121,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="35"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="34"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="33"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="32"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="74"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10539,10 +10878,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="31"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="30"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="29"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="28"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="70"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11040,10 +11379,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="95"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="94"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="93"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="92"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="137"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="136"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="135"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="134"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11764,10 +12103,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="27"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="26"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="25"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="24"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="66"/>
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13105,10 +13444,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K21">
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="23"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="64"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="62"/>
     <sortCondition descending="1" ref="I3:I21"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13813,10 +14152,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="103"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="102"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="101"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="100"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13879,7 +14218,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>48</v>
@@ -13890,10 +14229,12 @@
       <c r="G2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>7 (57%)</v>
+        <v>8 (63%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>186</v>
@@ -13922,10 +14263,12 @@
       <c r="G3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>6 (67%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>144</v>
@@ -13954,10 +14297,12 @@
       <c r="G4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I4" s="17" t="str" cm="1">
         <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
-        <v>6 (50%)</v>
+        <v>7 (43%)</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>161</v>
@@ -13986,10 +14331,12 @@
       <c r="G5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (67%)</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>186</v>
@@ -14016,10 +14363,12 @@
         <v>47</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="I6" s="17" t="str" cm="1">
         <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (67%)</v>
       </c>
       <c r="J6" s="21" t="s">
         <v>150</v>
@@ -14046,10 +14395,12 @@
       <c r="G7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I7" s="17" t="str" cm="1">
         <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
-        <v>5 (60%)</v>
+        <v>6 (50%)</v>
       </c>
       <c r="J7" s="21" t="s">
         <v>146</v>
@@ -14076,10 +14427,12 @@
       <c r="G8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I8" s="17" t="str" cm="1">
         <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
-        <v>5 (20%)</v>
+        <v>6 (17%)</v>
       </c>
       <c r="J8" s="21" t="s">
         <v>186</v>
@@ -14106,10 +14459,12 @@
       <c r="G9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="I9" s="17" t="str" cm="1">
         <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
-        <v>5 (100%)</v>
+        <v>6 (100%)</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>155</v>
@@ -14164,10 +14519,12 @@
       <c r="G11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="I11" s="18" t="str" cm="1">
         <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
-        <v>4 (50%)</v>
+        <v>5 (60%)</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>181</v>
@@ -14216,10 +14573,12 @@
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="I13" s="18" t="str" cm="1">
         <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
-        <v>3 (33%)</v>
+        <v>4 (50%)</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>148</v>
@@ -14268,7 +14627,9 @@
       <c r="J15" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="K15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="26" t="s">
@@ -14292,10 +14653,12 @@
       <c r="G16" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="12"/>
+      <c r="H16" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="I16" s="20" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>8 (50%)</v>
+        <v>9 (44%)</v>
       </c>
       <c r="J16" s="12" t="s">
         <v>219</v>
@@ -14318,6 +14681,588 @@
         <v>48</v>
       </c>
       <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="20" t="str" cm="1">
+        <f t="array" ref="I17">IF(COUNTA(B17:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B17:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B17:H17)-LEN(SUBSTITUTE(B17:H17,"W","")))/SUMPRODUCT(LEN(B17:H17)),"0%")&amp;")")</f>
+        <v>6 (33%)</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="3" t="str" cm="1">
+        <f t="array" ref="B18">IF(COUNTA(B2:B17)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B17)-LEN(SUBSTITUTE(B2:B17,"W","")))/SUMPRODUCT(LEN(B2:B17)),"0%")&amp;")")</f>
+        <v>12 (67%)</v>
+      </c>
+      <c r="C18" s="3" t="str" cm="1">
+        <f t="array" ref="C18">IF(COUNTA(C2:C17)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C17)-LEN(SUBSTITUTE(C2:C17,"W","")))/SUMPRODUCT(LEN(C2:C17)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="D18" s="3" t="str" cm="1">
+        <f t="array" ref="D18">IF(COUNTA(D2:D17)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D17)-LEN(SUBSTITUTE(D2:D17,"W","")))/SUMPRODUCT(LEN(D2:D17)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="E18" s="3" t="str" cm="1">
+        <f t="array" ref="E18">IF(COUNTA(E2:E17)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E17)-LEN(SUBSTITUTE(E2:E17,"W","")))/SUMPRODUCT(LEN(E2:E17)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="F18" s="3" t="str" cm="1">
+        <f t="array" ref="F18">IF(COUNTA(F2:F17)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F17)-LEN(SUBSTITUTE(F2:F17,"W","")))/SUMPRODUCT(LEN(F2:F17)),"0%")&amp;")")</f>
+        <v>12 (75%)</v>
+      </c>
+      <c r="G18" s="3" t="str" cm="1">
+        <f t="array" ref="G18">IF(COUNTA(G2:G17)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G17)-LEN(SUBSTITUTE(G2:G17,"W","")))/SUMPRODUCT(LEN(G2:G17)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="H18" s="3" t="str" cm="1">
+        <f t="array" ref="H18">IF(COUNTA(H2:H17)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H17)-LEN(SUBSTITUTE(H2:H17,"W","")))/SUMPRODUCT(LEN(H2:H17)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="I18" s="1" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B2:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H17)-LEN(SUBSTITUTE(B2:H17,"W","")))/SUMPRODUCT(LEN(B2:H17)),"0%")&amp;")")</f>
+        <v>84 (54%)</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="145"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="144"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="143"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="142"/>
+    <sortCondition descending="1" ref="I2:I17"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7A17C6-27E7-40A5-985D-664E5A3F58D7}">
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="17.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.4375" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B1" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="17" t="str" cm="1">
+        <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
+        <v>9 (33%)</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="17" t="str" cm="1">
+        <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
+        <v>7 (71%)</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="17" t="str" cm="1">
+        <f t="array" ref="I4">IF(COUNTA(B4:H4)=0,"0 (0%)",SUMPRODUCT(LEN(B4:H4))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B4:H4)-LEN(SUBSTITUTE(B4:H4,"W","")))/SUMPRODUCT(LEN(B4:H4)),"0%")&amp;")")</f>
+        <v>7 (71%)</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="17" t="str" cm="1">
+        <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
+        <v>6 (83%)</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="17" t="str" cm="1">
+        <f t="array" ref="I6">IF(COUNTA(B6:H6)=0,"0 (0%)",SUMPRODUCT(LEN(B6:H6))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B6:H6)-LEN(SUBSTITUTE(B6:H6,"W","")))/SUMPRODUCT(LEN(B6:H6)),"0%")&amp;")")</f>
+        <v>5 (60%)</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="17" t="str" cm="1">
+        <f t="array" ref="I7">IF(COUNTA(B7:H7)=0,"0 (0%)",SUMPRODUCT(LEN(B7:H7))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B7:H7)-LEN(SUBSTITUTE(B7:H7,"W","")))/SUMPRODUCT(LEN(B7:H7)),"0%")&amp;")")</f>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="17" t="str" cm="1">
+        <f t="array" ref="I8">IF(COUNTA(B8:H8)=0,"0 (0%)",SUMPRODUCT(LEN(B8:H8))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B8:H8)-LEN(SUBSTITUTE(B8:H8,"W","")))/SUMPRODUCT(LEN(B8:H8)),"0%")&amp;")")</f>
+        <v>5 (40%)</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="17" t="str" cm="1">
+        <f t="array" ref="I9">IF(COUNTA(B9:H9)=0,"0 (0%)",SUMPRODUCT(LEN(B9:H9))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B9:H9)-LEN(SUBSTITUTE(B9:H9,"W","")))/SUMPRODUCT(LEN(B9:H9)),"0%")&amp;")")</f>
+        <v>5 (20%)</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="19" t="str" cm="1">
+        <f t="array" ref="I10">IF(COUNTA(B10:H10)=0,"0 (0%)",SUMPRODUCT(LEN(B10:H10))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B10:H10)-LEN(SUBSTITUTE(B10:H10,"W","")))/SUMPRODUCT(LEN(B10:H10)),"0%")&amp;")")</f>
+        <v>4 (100%)</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="18" t="str" cm="1">
+        <f t="array" ref="I11">IF(COUNTA(B11:H11)=0,"0 (0%)",SUMPRODUCT(LEN(B11:H11))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B11:H11)-LEN(SUBSTITUTE(B11:H11,"W","")))/SUMPRODUCT(LEN(B11:H11)),"0%")&amp;")")</f>
+        <v>4 (50%)</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="18" t="str" cm="1">
+        <f t="array" ref="I12">IF(COUNTA(B12:H12)=0,"0 (0%)",SUMPRODUCT(LEN(B12:H12))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B12:H12)-LEN(SUBSTITUTE(B12:H12,"W","")))/SUMPRODUCT(LEN(B12:H12)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="18" t="str" cm="1">
+        <f t="array" ref="I13">IF(COUNTA(B13:H13)=0,"0 (0%)",SUMPRODUCT(LEN(B13:H13))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B13:H13)-LEN(SUBSTITUTE(B13:H13,"W","")))/SUMPRODUCT(LEN(B13:H13)),"0%")&amp;")")</f>
+        <v>3 (67%)</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="18" t="str" cm="1">
+        <f t="array" ref="I14">IF(COUNTA(B14:H14)=0,"0 (0%)",SUMPRODUCT(LEN(B14:H14))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B14:H14)-LEN(SUBSTITUTE(B14:H14,"W","")))/SUMPRODUCT(LEN(B14:H14)),"0%")&amp;")")</f>
+        <v>3 (33%)</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="18" t="str" cm="1">
+        <f t="array" ref="I15">IF(COUNTA(B15:H15)=0,"0 (0%)",SUMPRODUCT(LEN(B15:H15))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B15:H15)-LEN(SUBSTITUTE(B15:H15,"W","")))/SUMPRODUCT(LEN(B15:H15)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="20" t="str" cm="1">
+        <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
+        <v>10 (70%)</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="F17" s="5" t="s">
         <v>47</v>
       </c>
@@ -14330,60 +15275,108 @@
         <v>5 (40%)</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>247</v>
+        <v>189</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="20" t="str" cm="1">
+        <f t="array" ref="I18">IF(COUNTA(B18:H18)=0,"0 (0%)",SUMPRODUCT(LEN(B18:H18))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B18:H18)-LEN(SUBSTITUTE(B18:H18,"W","")))/SUMPRODUCT(LEN(B18:H18)),"0%")&amp;")")</f>
+        <v>1 (100%)</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="20" t="str" cm="1">
+        <f t="array" ref="I19">IF(COUNTA(B19:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B19:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B19:H19)-LEN(SUBSTITUTE(B19:H19,"W","")))/SUMPRODUCT(LEN(B19:H19)),"0%")&amp;")")</f>
+        <v>1 (0%)</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="3" t="str" cm="1">
-        <f t="array" ref="B18">IF(COUNTA(B2:B17)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B17)-LEN(SUBSTITUTE(B2:B17,"W","")))/SUMPRODUCT(LEN(B2:B17)),"0%")&amp;")")</f>
-        <v>12 (67%)</v>
-      </c>
-      <c r="C18" s="3" t="str" cm="1">
-        <f t="array" ref="C18">IF(COUNTA(C2:C17)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C17)-LEN(SUBSTITUTE(C2:C17,"W","")))/SUMPRODUCT(LEN(C2:C17)),"0%")&amp;")")</f>
+      <c r="B20" s="3" t="str" cm="1">
+        <f t="array" ref="B20">IF(COUNTA(B2:B19)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B19)-LEN(SUBSTITUTE(B2:B19,"W","")))/SUMPRODUCT(LEN(B2:B19)),"0%")&amp;")")</f>
         <v>12 (58%)</v>
       </c>
-      <c r="D18" s="3" t="str" cm="1">
-        <f t="array" ref="D18">IF(COUNTA(D2:D17)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D17)-LEN(SUBSTITUTE(D2:D17,"W","")))/SUMPRODUCT(LEN(D2:D17)),"0%")&amp;")")</f>
-        <v>12 (33%)</v>
-      </c>
-      <c r="E18" s="3" t="str" cm="1">
-        <f t="array" ref="E18">IF(COUNTA(E2:E17)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E17)-LEN(SUBSTITUTE(E2:E17,"W","")))/SUMPRODUCT(LEN(E2:E17)),"0%")&amp;")")</f>
+      <c r="C20" s="3" t="str" cm="1">
+        <f t="array" ref="C20">IF(COUNTA(C2:C19)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C19)-LEN(SUBSTITUTE(C2:C19,"W","")))/SUMPRODUCT(LEN(C2:C19)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="D20" s="3" t="str" cm="1">
+        <f t="array" ref="D20">IF(COUNTA(D2:D19)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D19)-LEN(SUBSTITUTE(D2:D19,"W","")))/SUMPRODUCT(LEN(D2:D19)),"0%")&amp;")")</f>
+        <v>12 (92%)</v>
+      </c>
+      <c r="E20" s="3" t="str" cm="1">
+        <f t="array" ref="E20">IF(COUNTA(E2:E19)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E19)-LEN(SUBSTITUTE(E2:E19,"W","")))/SUMPRODUCT(LEN(E2:E19)),"0%")&amp;")")</f>
+        <v>12 (42%)</v>
+      </c>
+      <c r="F20" s="3" t="str" cm="1">
+        <f t="array" ref="F20">IF(COUNTA(F2:F19)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F19)-LEN(SUBSTITUTE(F2:F19,"W","")))/SUMPRODUCT(LEN(F2:F19)),"0%")&amp;")")</f>
+        <v>12 (58%)</v>
+      </c>
+      <c r="G20" s="3" t="str" cm="1">
+        <f t="array" ref="G20">IF(COUNTA(G2:G19)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G19)-LEN(SUBSTITUTE(G2:G19,"W","")))/SUMPRODUCT(LEN(G2:G19)),"0%")&amp;")")</f>
         <v>12 (50%)</v>
       </c>
-      <c r="F18" s="3" t="str" cm="1">
-        <f t="array" ref="F18">IF(COUNTA(F2:F17)=0,"0 (0%)",SUMPRODUCT(LEN(F2:F17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(F2:F17)-LEN(SUBSTITUTE(F2:F17,"W","")))/SUMPRODUCT(LEN(F2:F17)),"0%")&amp;")")</f>
-        <v>12 (75%)</v>
-      </c>
-      <c r="G18" s="3" t="str" cm="1">
-        <f t="array" ref="G18">IF(COUNTA(G2:G17)=0,"0 (0%)",SUMPRODUCT(LEN(G2:G17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(G2:G17)-LEN(SUBSTITUTE(G2:G17,"W","")))/SUMPRODUCT(LEN(G2:G17)),"0%")&amp;")")</f>
-        <v>12 (42%)</v>
-      </c>
-      <c r="H18" s="3" t="str" cm="1">
-        <f t="array" ref="H18">IF(COUNTA(H2:H17)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H17)-LEN(SUBSTITUTE(H2:H17,"W","")))/SUMPRODUCT(LEN(H2:H17)),"0%")&amp;")")</f>
-        <v>0 (0%)</v>
-      </c>
-      <c r="I18" s="1" t="str" cm="1">
-        <f t="array" ref="I18">IF(COUNTA(B2:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H17)-LEN(SUBSTITUTE(B2:H17,"W","")))/SUMPRODUCT(LEN(B2:H17)),"0%")&amp;")")</f>
-        <v>72 (54%)</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="H20" s="3" t="str" cm="1">
+        <f t="array" ref="H20">IF(COUNTA(H2:H19)=0,"0 (0%)",SUMPRODUCT(LEN(H2:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(H2:H19)-LEN(SUBSTITUTE(H2:H19,"W","")))/SUMPRODUCT(LEN(H2:H19)),"0%")&amp;")")</f>
+        <v>12 (50%)</v>
+      </c>
+      <c r="I20" s="1" t="str" cm="1">
+        <f t="array" ref="I20">IF(COUNTA(B2:H19)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H19))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H19)-LEN(SUBSTITUTE(B2:H19,"W","")))/SUMPRODUCT(LEN(B2:H19)),"0%")&amp;")")</f>
+        <v>84 (56%)</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K20" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="4"/>
-    <sortCondition descending="1" ref="I2:I17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K20">
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="4"/>
+    <sortCondition descending="1" ref="I2:I20"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14971,10 +15964,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="91"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="90"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="133"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="132"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="131"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="130"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16274,10 +17267,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="87"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="86"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="84"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="129"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="128"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="127"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="126"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -16933,10 +17926,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="82"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="80"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="125"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="124"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="123"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="122"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -17637,10 +18630,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="78"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="76"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="121"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="120"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="119"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="118"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18272,10 +19265,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="74"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="72"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="117"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="116"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="115"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="114"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18960,10 +19953,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="70"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="68"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="113"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="112"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="111"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="110"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB24936A-EC29-4FD5-8E51-8B37159B6247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71B9258-8F77-476C-9E5D-86857182EA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="19" activeTab="24" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="19" activeTab="22" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
   <sheets>
     <sheet name="1월 3주차" sheetId="1" r:id="rId1"/>
@@ -1404,7 +1404,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="146">
+  <dxfs count="92">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1434,404 +1434,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF8ED973"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1A983"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8ED973"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3418,10 +3020,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="141"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="140"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="139"/>
-    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="138"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="87"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="85"/>
+    <sortCondition sortBy="cellColor" ref="I2:I19" dxfId="84"/>
     <sortCondition descending="1" ref="I2:I19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4072,10 +3674,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="109"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="108"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="107"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="106"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="55"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="54"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="53"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="52"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4766,10 +4368,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="105"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="104"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="103"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="102"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="51"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="50"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="49"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="48"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5481,10 +5083,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="101"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="100"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="99"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="98"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="47"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="46"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="45"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="44"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6250,10 +5852,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="97"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="96"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="95"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="94"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="43"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="42"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="41"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="40"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7025,10 +6627,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="93"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="92"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="91"/>
-    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="39"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="38"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="37"/>
+    <sortCondition descending="1" sortBy="cellColor" ref="I2:I25" dxfId="36"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7816,10 +7418,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="88"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="87"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="86"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="34"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="33"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="32"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8587,10 +8189,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="85"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="84"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="83"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="31"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="29"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="28"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9350,10 +8952,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="81"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="80"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="79"/>
-    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="27"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="26"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="25"/>
+    <sortCondition sortBy="cellColor" ref="J2:J25" dxfId="24"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10121,10 +9723,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="77"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="76"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="75"/>
-    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="23"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="I2:I25" dxfId="20"/>
     <sortCondition descending="1" ref="I2:I25"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10878,10 +10480,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="73"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="72"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="71"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="16"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11379,10 +10981,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="137"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="136"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="135"/>
-    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="134"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="83"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="82"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="81"/>
+    <sortCondition sortBy="cellColor" ref="B2:B18" dxfId="80"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12103,10 +11705,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K23">
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="69"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="68"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="67"/>
-    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="I3:I23" dxfId="12"/>
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13444,10 +13046,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K21">
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="65"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="64"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="63"/>
-    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="I3:I21" dxfId="8"/>
     <sortCondition descending="1" ref="I3:I21"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13608,7 +13210,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>47</v>
@@ -13630,7 +13232,7 @@
       </c>
       <c r="I5" s="17" t="str" cm="1">
         <f t="array" ref="I5">IF(COUNTA(B5:H5)=0,"0 (0%)",SUMPRODUCT(LEN(B5:H5))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B5:H5)-LEN(SUBSTITUTE(B5:H5,"W","")))/SUMPRODUCT(LEN(B5:H5)),"0%")&amp;")")</f>
-        <v>7 (43%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>144</v>
@@ -14115,7 +13717,7 @@
       </c>
       <c r="B23" s="3" t="str" cm="1">
         <f t="array" ref="B23">IF(COUNTA(B2:B22)=0,"0 (0%)",SUMPRODUCT(LEN(B2:B22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:B22)-LEN(SUBSTITUTE(B2:B22,"W","")))/SUMPRODUCT(LEN(B2:B22)),"0%")&amp;")")</f>
-        <v>12 (33%)</v>
+        <v>12 (42%)</v>
       </c>
       <c r="C23" s="3" t="str" cm="1">
         <f t="array" ref="C23">IF(COUNTA(C2:C22)=0,"0 (0%)",SUMPRODUCT(LEN(C2:C22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(C2:C22)-LEN(SUBSTITUTE(C2:C22,"W","")))/SUMPRODUCT(LEN(C2:C22)),"0%")&amp;")")</f>
@@ -14143,7 +13745,7 @@
       </c>
       <c r="I23" s="1" t="str" cm="1">
         <f t="array" ref="I23">IF(COUNTA(B2:H22)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H22))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H22)-LEN(SUBSTITUTE(B2:H22,"W","")))/SUMPRODUCT(LEN(B2:H22)),"0%")&amp;")")</f>
-        <v>84 (52%)</v>
+        <v>84 (54%)</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>132</v>
@@ -14152,10 +13754,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="61"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="60"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="59"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14744,10 +14346,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="145"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="144"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="143"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="142"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I17"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14838,7 +14440,7 @@
         <v>277</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>48</v>
@@ -14860,7 +14462,7 @@
       </c>
       <c r="I3" s="17" t="str" cm="1">
         <f t="array" ref="I3">IF(COUNTA(B3:H3)=0,"0 (0%)",SUMPRODUCT(LEN(B3:H3))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B3:H3)-LEN(SUBSTITUTE(B3:H3,"W","")))/SUMPRODUCT(LEN(B3:H3)),"0%")&amp;")")</f>
-        <v>7 (71%)</v>
+        <v>7 (57%)</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>144</v>
@@ -15218,7 +14820,7 @@
         <v>221</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>67</v>
@@ -15240,7 +14842,7 @@
       </c>
       <c r="I16" s="20" t="str" cm="1">
         <f t="array" ref="I16">IF(COUNTA(B16:H16)=0,"0 (0%)",SUMPRODUCT(LEN(B16:H16))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B16:H16)-LEN(SUBSTITUTE(B16:H16,"W","")))/SUMPRODUCT(LEN(B16:H16)),"0%")&amp;")")</f>
-        <v>10 (70%)</v>
+        <v>10 (80%)</v>
       </c>
       <c r="J16" s="12" t="s">
         <v>318</v>
@@ -15372,10 +14974,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K20">
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="88"/>
     <sortCondition descending="1" ref="I2:I20"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -15964,10 +15566,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="133"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="132"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="131"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="130"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="79"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="78"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="77"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="76"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -17267,10 +16869,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="129"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="128"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="127"/>
-    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="126"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="74"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="73"/>
+    <sortCondition sortBy="cellColor" ref="I2:I27" dxfId="72"/>
     <sortCondition descending="1" ref="I2:I27"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -17926,10 +17528,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="125"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="124"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="123"/>
-    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="122"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="71"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="70"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="69"/>
+    <sortCondition sortBy="cellColor" ref="I2:I24" dxfId="68"/>
     <sortCondition descending="1" ref="I2:I24"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18630,10 +18232,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="121"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="120"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="119"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="118"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="67"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="66"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="65"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="64"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -19265,10 +18867,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="117"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="116"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="115"/>
-    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="114"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="63"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="62"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="61"/>
+    <sortCondition sortBy="cellColor" ref="I2:I23" dxfId="60"/>
     <sortCondition descending="1" ref="I2:I23"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -19953,10 +19555,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="113"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="112"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="111"/>
-    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="110"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="59"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="57"/>
+    <sortCondition sortBy="cellColor" ref="I2:I26" dxfId="56"/>
     <sortCondition descending="1" ref="I2:I26"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/길랭 (version 1).xlsx
+++ b/data/길랭 (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifcat\OneDrive\ekdnsfhem\GitHub\Romang\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71B9258-8F77-476C-9E5D-86857182EA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23333A04-8574-41B2-9E14-F0BA6986C0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="19" activeTab="22" xr2:uid="{3631474B-DFC9-4597-8BEB-4EEAC2453A81}"/>
   </bookViews>
@@ -13754,10 +13754,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="91"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="90"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="89"/>
+    <sortCondition sortBy="cellColor" ref="I2:I22" dxfId="88"/>
     <sortCondition descending="1" ref="I2:I22"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13820,7 +13820,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>48</v>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="I2" s="17" t="str" cm="1">
         <f t="array" ref="I2">IF(COUNTA(B2:H2)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H2))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H2)-LEN(SUBSTITUTE(B2:H2,"W","")))/SUMPRODUCT(LEN(B2:H2)),"0%")&amp;")")</f>
-        <v>8 (63%)</v>
+        <v>8 (50%)</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>186</v>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D18" s="3" t="str" cm="1">
         <f t="array" ref="D18">IF(COUNTA(D2:D17)=0,"0 (0%)",SUMPRODUCT(LEN(D2:D17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(D2:D17)-LEN(SUBSTITUTE(D2:D17,"W","")))/SUMPRODUCT(LEN(D2:D17)),"0%")&amp;")")</f>
-        <v>12 (42%)</v>
+        <v>12 (33%)</v>
       </c>
       <c r="E18" s="3" t="str" cm="1">
         <f t="array" ref="E18">IF(COUNTA(E2:E17)=0,"0 (0%)",SUMPRODUCT(LEN(E2:E17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(E2:E17)-LEN(SUBSTITUTE(E2:E17,"W","")))/SUMPRODUCT(LEN(E2:E17)),"0%")&amp;")")</f>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="I18" s="1" t="str" cm="1">
         <f t="array" ref="I18">IF(COUNTA(B2:H17)=0,"0 (0%)",SUMPRODUCT(LEN(B2:H17))&amp;" ("&amp;TEXT(SUMPRODUCT(LEN(B2:H17)-LEN(SUBSTITUTE(B2:H17,"W","")))/SUMPRODUCT(LEN(B2:H17)),"0%")&amp;")")</f>
-        <v>84 (54%)</v>
+        <v>84 (52%)</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>132</v>
@@ -14346,10 +14346,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="3"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="2"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="1"/>
-    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="7"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="6"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="I2:I17" dxfId="4"/>
     <sortCondition descending="1" ref="I2:I17"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14974,10 +14974,10 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K20">
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="91"/>
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="90"/>
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="89"/>
-    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="88"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="3"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="2"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="I2:I20" dxfId="0"/>
     <sortCondition descending="1" ref="I2:I20"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
